--- a/src/main/resources/SistemasBasura.xlsx
+++ b/src/main/resources/SistemasBasura.xlsx
@@ -5,39 +5,28 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\Practica 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\practica 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F36DD1-3C4E-4A38-B51C-8EE7D69021F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9513E76-EF12-46C9-927B-1E91F828EF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FF8BD292-BC82-4648-93FB-5EF5760864FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Contribuyente" sheetId="1" r:id="rId1"/>
     <sheet name="Ordenanza" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="693">
   <si>
     <t>Nombre</t>
   </si>
@@ -1581,13 +1570,19 @@
     <t>85550564726165145618</t>
   </si>
   <si>
+    <t>12 13 14 25</t>
+  </si>
+  <si>
+    <t>16 17 18 19</t>
+  </si>
+  <si>
     <t>31645124453461205100</t>
   </si>
   <si>
     <t>DK8231645124453461205100</t>
   </si>
   <si>
-    <t>jmd00@tasabasura2026.com</t>
+    <t>JMD00@tasabasura2026.com</t>
   </si>
   <si>
     <t>65614874115615445600</t>
@@ -1596,97 +1591,79 @@
     <t>ES4865614874115615445600</t>
   </si>
   <si>
-    <t>rfm00@tasabasura2026.com</t>
+    <t>RFM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>32569523086220165100</t>
   </si>
   <si>
-    <t>RO0232569523086220165100</t>
+    <t/>
   </si>
   <si>
     <t>DE7424561937521546497521</t>
   </si>
   <si>
-    <t>aln00@tasabasura2026.com</t>
+    <t>ALN00@tasabasura2026.com</t>
   </si>
   <si>
     <t>MC6436520125638451012515</t>
   </si>
   <si>
-    <t>rgo00@tasabasura2026.com</t>
+    <t>RGO00@tasabasura2026.com</t>
   </si>
   <si>
     <t>GR9420125003305201112544</t>
   </si>
   <si>
-    <t>vdo00@tasabasura2026.com</t>
+    <t>VDO00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES2821651484690980008984</t>
   </si>
   <si>
-    <t>vbp00@tasabasura2026.com</t>
+    <t>VBP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>FI5620960043043554600000</t>
   </si>
   <si>
-    <t>abp00@tasabasura2026.com</t>
+    <t>ABP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>21564975263245467900</t>
   </si>
   <si>
-    <t>ES9521564975263245467900</t>
-  </si>
-  <si>
     <t>LT2132566221532587754888</t>
   </si>
   <si>
-    <t>acp00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>EE2023215465315456411515</t>
-  </si>
-  <si>
-    <t>SM1325894363415485700777</t>
-  </si>
-  <si>
-    <t>ES0396431245188150005111</t>
+    <t>ACP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>25030000194574745400</t>
   </si>
   <si>
-    <t>AT7125030000194574745400</t>
-  </si>
-  <si>
-    <t>IT2115953684881254695211</t>
-  </si>
-  <si>
     <t>DK2500750184330702510011</t>
   </si>
   <si>
-    <t>cis00@tasabasura2026.com</t>
+    <t>CIS00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES7423455254983263234411</t>
   </si>
   <si>
-    <t>mq00@tasabasura2026.com</t>
+    <t>MQ00@tasabasura2026.com</t>
   </si>
   <si>
     <t>GR4920910936583000000000</t>
   </si>
   <si>
-    <t>bv00@tasabasura2026.com</t>
+    <t>BV00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES0420960043052159000011</t>
   </si>
   <si>
-    <t>pp00@tasabasura2026.com</t>
+    <t>PP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>12669681125112121200</t>
@@ -1695,31 +1672,31 @@
     <t>DE6912669681125112121200</t>
   </si>
   <si>
-    <t>pc00@tasabasura2026.com</t>
+    <t>PC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES2956187775315550000651</t>
   </si>
   <si>
-    <t>gmm00@tasabasura2026.com</t>
+    <t>GMM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES0425516848021156151054</t>
   </si>
   <si>
-    <t>cgm00@tasabasura2026.com</t>
+    <t>CGM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES4534698752714600549403</t>
   </si>
   <si>
-    <t>csn00@tasabasura2026.com</t>
+    <t>CSN00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES2766649444162310000255</t>
   </si>
   <si>
-    <t>alo00@tasabasura2026.com</t>
+    <t>ALO00@tasabasura2026.com</t>
   </si>
   <si>
     <t>23185484415641685908</t>
@@ -1728,88 +1705,85 @@
     <t>FR8423185484415641685908</t>
   </si>
   <si>
-    <t>gmm01@tasabasura2026.com</t>
+    <t>GMM01@tasabasura2026.com</t>
   </si>
   <si>
     <t>DE5021508149175421346497</t>
   </si>
   <si>
-    <t>tcp00@tasabasura2026.com</t>
+    <t>TCP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>DE6721346154503164978451</t>
   </si>
   <si>
-    <t>ccp00@tasabasura2026.com</t>
+    <t>CCP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES7225187786311225455548</t>
   </si>
   <si>
-    <t>cap00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES6423164897642213030600</t>
+    <t>CAP00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES2396536214865214585214</t>
   </si>
   <si>
-    <t>elr00@tasabasura2026.com</t>
+    <t>ELR00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES6885461325251978750005</t>
   </si>
   <si>
-    <t>dlr00@tasabasura2026.com</t>
+    <t>DLR00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES5020960043073071400000</t>
   </si>
   <si>
-    <t>spr00@tasabasura2026.com</t>
+    <t>SPR00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES8220960043042158800000</t>
   </si>
   <si>
-    <t>gpr00@tasabasura2026.com</t>
+    <t>GPR00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES7521654587985156484454</t>
   </si>
   <si>
-    <t>sas00@tasabasura2026.com</t>
+    <t>SAS00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES8451651681961210656544</t>
   </si>
   <si>
-    <t>bfs00@tasabasura2026.com</t>
+    <t>BFS00@tasabasura2026.com</t>
   </si>
   <si>
     <t>GB9720910936583000000000</t>
   </si>
   <si>
-    <t>gmg00@tasabasura2026.com</t>
+    <t>GMG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>DE9301821135910205540000</t>
   </si>
   <si>
-    <t>mlg00@tasabasura2026.com</t>
+    <t>MLG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>DE7822631245526916432102</t>
   </si>
   <si>
-    <t>iag00@tasabasura2026.com</t>
+    <t>IAG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES2120960043043075700000</t>
   </si>
   <si>
-    <t>iag01@tasabasura2026.com</t>
+    <t>IAG01@tasabasura2026.com</t>
   </si>
   <si>
     <t>25635478301002541233</t>
@@ -1818,7 +1792,7 @@
     <t>SM7825635478301002541233</t>
   </si>
   <si>
-    <t>gpg00@tasabasura2026.com</t>
+    <t>GPG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>32154697155423121012</t>
@@ -1827,10 +1801,7 @@
     <t>ES8932154697155423121012</t>
   </si>
   <si>
-    <t>rgg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>GR3836521452736500658485</t>
+    <t>RGG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20008521588775113327</t>
@@ -1839,7 +1810,7 @@
     <t>GB5720008521588775113327</t>
   </si>
   <si>
-    <t>afg00@tasabasura2026.com</t>
+    <t>AFG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20960043073000100018</t>
@@ -1848,13 +1819,13 @@
     <t>ES2520960043073000100018</t>
   </si>
   <si>
-    <t>apm00@tasabasura2026.com</t>
+    <t>APM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>GB0836585214290025478551</t>
   </si>
   <si>
-    <t>gmm02@tasabasura2026.com</t>
+    <t>GMM02@tasabasura2026.com</t>
   </si>
   <si>
     <t>12548523445214585218</t>
@@ -1863,25 +1834,25 @@
     <t>ES0912548523445214585218</t>
   </si>
   <si>
-    <t>alm00@tasabasura2026.com</t>
+    <t>ALM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES6931624561042546920007</t>
   </si>
   <si>
-    <t>ldm00@tasabasura2026.com</t>
+    <t>LDM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES1436154231712500312566</t>
   </si>
   <si>
-    <t>ad00@tasabasura2026.com</t>
+    <t>AD00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES8244875664127231645789</t>
   </si>
   <si>
-    <t>lr00@tasabasura2026.com</t>
+    <t>LR00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20960031482124800018</t>
@@ -1890,25 +1861,19 @@
     <t>ES2420960031482124800018</t>
   </si>
   <si>
-    <t>lc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES1633620012937852100256</t>
+    <t>LC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES1933218885441445121022</t>
   </si>
   <si>
-    <t>afg01@tasabasura2026.com</t>
+    <t>AFG01@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES8462581542713690044508</t>
   </si>
   <si>
-    <t>dgg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES0725165151118666365191</t>
+    <t>DGG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20960043023000100021</t>
@@ -1917,13 +1882,13 @@
     <t>ES6020960043023000100021</t>
   </si>
   <si>
-    <t>sog00@tasabasura2026.com</t>
+    <t>SOG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>PT3536952365020014425254</t>
   </si>
   <si>
-    <t>vvg00@tasabasura2026.com</t>
+    <t>VVG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>65168874681561561522</t>
@@ -1932,13 +1897,13 @@
     <t>ES2965168874681561561522</t>
   </si>
   <si>
-    <t>vmg00@tasabasura2026.com</t>
+    <t>VMG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES3220960583831234500000</t>
   </si>
   <si>
-    <t>mbg00@tasabasura2026.com</t>
+    <t>MBG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>21416325801510005527</t>
@@ -1947,25 +1912,19 @@
     <t>ES7421416325801510005527</t>
   </si>
   <si>
-    <t>cbg00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>LU0932628484504115151115</t>
+    <t>CBG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20960056143231500032</t>
   </si>
   <si>
-    <t>ES6620960056143231500032</t>
-  </si>
-  <si>
     <t>63516541858944000993</t>
   </si>
   <si>
     <t>ES4063516541858944000993</t>
   </si>
   <si>
-    <t>sdm00@tasabasura2026.com</t>
+    <t>SDM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>23658965294585223213</t>
@@ -1974,13 +1933,13 @@
     <t>ES2923658965294585223213</t>
   </si>
   <si>
-    <t>egm00@tasabasura2026.com</t>
+    <t>EGM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>FI6132658012367712548745</t>
   </si>
   <si>
-    <t>gpm00@tasabasura2026.com</t>
+    <t>GPM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>23652365132254222021</t>
@@ -1989,31 +1948,28 @@
     <t>ES5223652365132254222021</t>
   </si>
   <si>
-    <t>eam00@tasabasura2026.com</t>
+    <t>EAM00@tasabasura2026.com</t>
   </si>
   <si>
     <t>20012541120023365296</t>
   </si>
   <si>
-    <t>FR7520012541120023365296</t>
-  </si>
-  <si>
     <t>ES9232584216971684051000</t>
   </si>
   <si>
-    <t>mg00@tasabasura2026.com</t>
+    <t>MG00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES7395485212315484010000</t>
   </si>
   <si>
-    <t>jac00@tasabasura2026.com</t>
+    <t>JAC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>LT9321856333126985542360</t>
   </si>
   <si>
-    <t>bdc00@tasabasura2026.com</t>
+    <t>BDC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>36245978123245679018</t>
@@ -2022,7 +1978,7 @@
     <t>ES4836245978123245679018</t>
   </si>
   <si>
-    <t>ngc00@tasabasura2026.com</t>
+    <t>NGC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>31245164126597845172</t>
@@ -2031,16 +1987,13 @@
     <t>ES3331245164126597845172</t>
   </si>
   <si>
-    <t>mlc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>SM4423221158252545471411</t>
+    <t>MLC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>SE6832574512085411002255</t>
   </si>
   <si>
-    <t>mlc01@tasabasura2026.com</t>
+    <t>MLC01@tasabasura2026.com</t>
   </si>
   <si>
     <t>20960043093468900021</t>
@@ -2049,7 +2002,7 @@
     <t>ES4820960043093468900021</t>
   </si>
   <si>
-    <t>cfc00@tasabasura2026.com</t>
+    <t>CFC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>31215643895060225039</t>
@@ -2058,19 +2011,19 @@
     <t>ES9831215643895060225039</t>
   </si>
   <si>
-    <t>cgc00@tasabasura2026.com</t>
+    <t>CGC00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>0.0</t>
   </si>
   <si>
     <t>85550564796165145618</t>
   </si>
   <si>
-    <t>AT6185550564796165145618</t>
-  </si>
-  <si>
     <t>ES1665165654918886005001</t>
   </si>
   <si>
-    <t>ksc00@tasabasura2026.com</t>
+    <t>KSC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>65645150815168448846</t>
@@ -2079,22 +2032,19 @@
     <t>AT9465645150815168448846</t>
   </si>
   <si>
-    <t>mhc00@tasabasura2026.com</t>
+    <t>MHC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>IT3526551681807651415636</t>
   </si>
   <si>
-    <t>cld00@tasabasura2026.com</t>
+    <t>CLD00@tasabasura2026.com</t>
   </si>
   <si>
     <t>HU2399558741836555551120</t>
   </si>
   <si>
-    <t>mfd00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES4352198484752100515144</t>
+    <t>MFD00@tasabasura2026.com</t>
   </si>
   <si>
     <t>51556584261251000242</t>
@@ -2103,16 +2053,13 @@
     <t>IE4751556584261251000242</t>
   </si>
   <si>
-    <t>gmm03@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>DK9032541112811220000588</t>
+    <t>GMM03@tasabasura2026.com</t>
   </si>
   <si>
     <t>LT9362541122421110105611</t>
   </si>
   <si>
-    <t>dmc00@tasabasura2026.com</t>
+    <t>DMC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>55065688711051056112</t>
@@ -2121,49 +2068,43 @@
     <t>ES9255065688711051056112</t>
   </si>
   <si>
-    <t>ebc00@tasabasura2026.com</t>
-  </si>
-  <si>
-    <t>ES7426221011628048788896</t>
+    <t>EBC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES9712548521518742146695</t>
   </si>
   <si>
-    <t>msc00@tasabasura2026.com</t>
+    <t>MSC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES9001826530120201560000</t>
   </si>
   <si>
-    <t>mdc00@tasabasura2026.com</t>
+    <t>MDC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES9021651651812511133551</t>
   </si>
   <si>
-    <t>mfc00@tasabasura2026.com</t>
+    <t>MFC00@tasabasura2026.com</t>
   </si>
   <si>
     <t>ES6851651487910005118185</t>
   </si>
   <si>
-    <t>cdd00@tasabasura2026.com</t>
+    <t>CDD00@tasabasura2026.com</t>
   </si>
   <si>
     <t>36250012834785523317</t>
   </si>
   <si>
-    <t>CZ4136250012834785523317</t>
-  </si>
-  <si>
     <t>22515651985640081019</t>
   </si>
   <si>
     <t>AT5422515651985640081019</t>
   </si>
   <si>
-    <t>hpd00@tasabasura2026.com</t>
+    <t>HPD00@tasabasura2026.com</t>
   </si>
 </sst>
 </file>
@@ -2538,18 +2479,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C6ACB8-7F34-425E-9257-91AD8B97F35F}">
-  <dimension ref="A1:P152"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R152"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="30.140625"/>
-    <col min="2" max="2" customWidth="true" style="5" width="30.140625"/>
-    <col min="8" max="8" customWidth="true" width="22.5703125"/>
+    <col min="1" max="1" customWidth="true" width="30.109375"/>
+    <col min="2" max="2" customWidth="true" style="5" width="30.109375"/>
+    <col min="8" max="8" customWidth="true" width="22.5546875"/>
     <col min="13" max="13" customWidth="true" width="14.0"/>
-    <col min="14" max="14" style="7" width="11.42578125"/>
-    <col min="16" max="16" style="1" width="11.42578125"/>
+    <col min="14" max="14" style="7" width="11.44140625"/>
+    <col min="16" max="16" style="1" width="11.44140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s" s="0">
         <v>4</v>
       </c>
@@ -2599,7 +2540,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s" s="0">
         <v>313</v>
       </c>
@@ -2622,31 +2563,34 @@
         <v>461</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I2" t="s" s="0">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J2" t="s" s="0">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K2" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L2" s="0">
-        <v>0</v>
-      </c>
-      <c r="M2" s="0">
-        <v>251</v>
-      </c>
-      <c r="N2" s="7">
-        <v>45294</v>
+      <c r="L2" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M2" t="n" s="0">
+        <v>251.0</v>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>45294.0</v>
+      </c>
+      <c r="O2" s="7" t="n">
+        <v>45717.0</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>314</v>
       </c>
@@ -2669,31 +2613,34 @@
         <v>462</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I3" t="s" s="0">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J3" t="s" s="0">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K3" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L3" s="0">
-        <v>0</v>
-      </c>
-      <c r="M3" s="0">
-        <v>100</v>
-      </c>
-      <c r="N3" s="7">
-        <v>38267</v>
+      <c r="L3" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>38267.0</v>
+      </c>
+      <c r="O3" s="7" t="n">
+        <v>45718.0</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>314</v>
       </c>
@@ -2716,28 +2663,31 @@
         <v>442</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I4" t="s" s="0">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K4" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L4" s="0">
-        <v>50</v>
-      </c>
-      <c r="M4" s="0">
-        <v>298</v>
-      </c>
-      <c r="N4" s="7">
-        <v>39682</v>
+      <c r="L4" s="0" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>298.0</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>39682.0</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>45719.0</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>315</v>
       </c>
@@ -2763,28 +2713,31 @@
         <v>244</v>
       </c>
       <c r="I5" t="s" s="0">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="K5" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="L5" s="0">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0">
-        <v>308</v>
-      </c>
-      <c r="N5" s="7">
-        <v>38765</v>
+      <c r="L5" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>308.0</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>38765.0</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <v>45720.0</v>
       </c>
       <c r="P5" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>316</v>
       </c>
@@ -2810,28 +2763,31 @@
         <v>245</v>
       </c>
       <c r="I6" t="s" s="0">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K6" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L6" s="0">
-        <v>25</v>
-      </c>
-      <c r="M6" s="0">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>38646</v>
+      <c r="L6" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>38646.0</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <v>45721.0</v>
       </c>
       <c r="P6" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>317</v>
       </c>
@@ -2868,11 +2824,14 @@
       <c r="N7" s="7">
         <v>41039</v>
       </c>
+      <c r="O7" s="7">
+        <v>45722</v>
+      </c>
       <c r="P7" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>318</v>
       </c>
@@ -2898,28 +2857,31 @@
         <v>246</v>
       </c>
       <c r="I8" t="s" s="0">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J8" t="s" s="0">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K8" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L8" s="0">
-        <v>25</v>
-      </c>
-      <c r="M8" s="0">
-        <v>51</v>
-      </c>
-      <c r="N8" s="7">
-        <v>45738</v>
+      <c r="L8" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>45738.0</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <v>45723.0</v>
       </c>
       <c r="P8" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>319</v>
       </c>
@@ -2945,28 +2907,31 @@
         <v>247</v>
       </c>
       <c r="I9" t="s" s="0">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J9" t="s" s="0">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K9" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L9" s="0">
-        <v>0</v>
-      </c>
-      <c r="M9" s="0">
-        <v>137</v>
-      </c>
-      <c r="N9" s="7">
-        <v>45739</v>
+      <c r="L9" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>137.0</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>45739.0</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>45724.0</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>320</v>
       </c>
@@ -2992,28 +2957,31 @@
         <v>248</v>
       </c>
       <c r="I10" t="s" s="0">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J10" t="s" s="0">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K10" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L10" s="0">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0">
-        <v>43</v>
-      </c>
-      <c r="N10" s="7">
-        <v>45740</v>
+      <c r="L10" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>45740.0</v>
+      </c>
+      <c r="O10" s="7" t="n">
+        <v>45725.0</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>320</v>
       </c>
@@ -3036,28 +3004,31 @@
         <v>465</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="I11" t="s" s="0">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="K11" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L11" s="0">
-        <v>25</v>
-      </c>
-      <c r="M11" s="0">
-        <v>187</v>
-      </c>
-      <c r="N11" s="7">
-        <v>45709</v>
+      <c r="L11" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>45709.0</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>45726.0</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>320</v>
       </c>
@@ -3083,28 +3054,31 @@
         <v>430</v>
       </c>
       <c r="I12" t="s" s="0">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J12" t="s" s="0">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K12" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L12" s="0">
-        <v>0</v>
-      </c>
-      <c r="M12" s="0">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
-        <v>45710</v>
+      <c r="L12" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>45710.0</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>45727.0</v>
       </c>
       <c r="P12" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>320</v>
       </c>
@@ -3130,25 +3104,28 @@
         <v>249</v>
       </c>
       <c r="I13" t="s" s="0">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="K13" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L13" s="0">
-        <v>0</v>
-      </c>
-      <c r="M13" s="0">
-        <v>179</v>
-      </c>
-      <c r="N13" s="7">
-        <v>45873</v>
+      <c r="L13" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <v>179.0</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>45873.0</v>
+      </c>
+      <c r="O13" s="7" t="n">
+        <v>45728.0</v>
       </c>
       <c r="P13" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>318</v>
       </c>
@@ -3185,17 +3162,20 @@
       <c r="N14" s="7">
         <v>45976</v>
       </c>
+      <c r="O14" s="7">
+        <v>45729</v>
+      </c>
       <c r="P14" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="6"/>
       <c r="G15" s="1"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>322</v>
       </c>
@@ -3220,9 +3200,6 @@
       <c r="H16" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="I16" t="s" s="0">
-        <v>537</v>
-      </c>
       <c r="K16" t="s" s="0">
         <v>241</v>
       </c>
@@ -3235,11 +3212,12 @@
       <c r="N16" s="7">
         <v>40637</v>
       </c>
+      <c r="O16" s="7"/>
       <c r="P16" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>323</v>
       </c>
@@ -3264,9 +3242,6 @@
       <c r="H17" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="I17" t="s" s="0">
-        <v>538</v>
-      </c>
       <c r="K17" t="s" s="0">
         <v>241</v>
       </c>
@@ -3279,11 +3254,12 @@
       <c r="N17" s="7">
         <v>45810</v>
       </c>
+      <c r="O17" s="7"/>
       <c r="P17" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>323</v>
       </c>
@@ -3306,28 +3282,29 @@
         <v>439</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="I18" t="s" s="0">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="K18" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L18" s="0">
-        <v>0</v>
-      </c>
-      <c r="M18" s="0">
-        <v>122</v>
-      </c>
-      <c r="N18" s="7">
-        <v>45939</v>
-      </c>
+      <c r="L18" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>45939.0</v>
+      </c>
+      <c r="O18" s="7"/>
       <c r="P18" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>322</v>
       </c>
@@ -3352,9 +3329,6 @@
       <c r="H19" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="I19" t="s" s="0">
-        <v>541</v>
-      </c>
       <c r="K19" t="s" s="0">
         <v>241</v>
       </c>
@@ -3367,11 +3341,12 @@
       <c r="N19" s="7">
         <v>45946</v>
       </c>
+      <c r="O19" s="7"/>
       <c r="P19" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>322</v>
       </c>
@@ -3408,11 +3383,12 @@
       <c r="N20" s="7">
         <v>45778</v>
       </c>
+      <c r="O20" s="7"/>
       <c r="P20" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>323</v>
       </c>
@@ -3438,28 +3414,29 @@
         <v>434</v>
       </c>
       <c r="I21" t="s" s="0">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="J21" t="s" s="0">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="K21" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L21" s="0">
-        <v>0</v>
-      </c>
-      <c r="M21" s="0">
-        <v>122</v>
-      </c>
-      <c r="N21" s="7">
-        <v>45627</v>
-      </c>
+      <c r="L21" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>45627.0</v>
+      </c>
+      <c r="O21" s="7"/>
       <c r="P21" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>324</v>
       </c>
@@ -3482,28 +3459,29 @@
         <v>435</v>
       </c>
       <c r="I22" t="s" s="0">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="J22" t="s" s="0">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="K22" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L22" s="0">
-        <v>25</v>
-      </c>
-      <c r="M22" s="0">
-        <v>74</v>
-      </c>
-      <c r="N22" s="7">
-        <v>45628</v>
-      </c>
+      <c r="L22" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>45628.0</v>
+      </c>
+      <c r="O22" s="7"/>
       <c r="P22" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>320</v>
       </c>
@@ -3526,28 +3504,29 @@
         <v>250</v>
       </c>
       <c r="I23" t="s" s="0">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="J23" t="s" s="0">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="K23" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L23" s="0">
-        <v>0</v>
-      </c>
-      <c r="M23" s="0">
-        <v>200</v>
-      </c>
-      <c r="N23" s="7">
-        <v>45629</v>
-      </c>
+      <c r="L23" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>45629.0</v>
+      </c>
+      <c r="O23" s="7"/>
       <c r="P23" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>320</v>
       </c>
@@ -3570,28 +3549,29 @@
         <v>436</v>
       </c>
       <c r="I24" t="s" s="0">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J24" t="s" s="0">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="K24" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L24" s="0">
-        <v>0</v>
-      </c>
-      <c r="M24" s="0">
-        <v>177</v>
-      </c>
-      <c r="N24" s="7">
-        <v>45630</v>
-      </c>
+      <c r="L24" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>177.0</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>45630.0</v>
+      </c>
+      <c r="O24" s="7"/>
       <c r="P24" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>323</v>
       </c>
@@ -3611,37 +3591,38 @@
         <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="I25" t="s" s="0">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="J25" t="s" s="0">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="K25" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L25" s="0">
-        <v>25</v>
-      </c>
-      <c r="M25" s="0">
-        <v>42</v>
-      </c>
-      <c r="N25" s="7">
-        <v>45631</v>
-      </c>
+      <c r="L25" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>45631.0</v>
+      </c>
+      <c r="O25" s="7"/>
       <c r="P25" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="6"/>
       <c r="G26" s="1"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>320</v>
       </c>
@@ -3667,31 +3648,29 @@
         <v>251</v>
       </c>
       <c r="I27" t="s" s="0">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="J27" t="s" s="0">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="K27" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L27" s="0">
-        <v>0</v>
-      </c>
-      <c r="M27" s="0">
-        <v>88</v>
-      </c>
-      <c r="N27" s="7">
-        <v>39525</v>
-      </c>
-      <c r="O27" s="7">
-        <v>45352</v>
-      </c>
+      <c r="L27" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <v>46023.0</v>
+      </c>
+      <c r="O27" s="7"/>
       <c r="P27" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>317</v>
       </c>
@@ -3717,31 +3696,29 @@
         <v>252</v>
       </c>
       <c r="I28" t="s" s="0">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="J28" t="s" s="0">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="K28" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L28" s="0">
-        <v>25</v>
-      </c>
-      <c r="M28" s="0">
-        <v>101</v>
-      </c>
-      <c r="N28" s="7">
-        <v>42667</v>
-      </c>
-      <c r="O28" s="7">
-        <v>45353</v>
-      </c>
+      <c r="L28" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>46024.0</v>
+      </c>
+      <c r="O28" s="7"/>
       <c r="P28" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>318</v>
       </c>
@@ -3776,16 +3753,14 @@
         <v>10</v>
       </c>
       <c r="N29" s="7">
-        <v>44639</v>
-      </c>
-      <c r="O29" s="7">
-        <v>45354</v>
-      </c>
+        <v>46025</v>
+      </c>
+      <c r="O29" s="7"/>
       <c r="P29" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>318</v>
       </c>
@@ -3811,31 +3786,29 @@
         <v>253</v>
       </c>
       <c r="I30" t="s" s="0">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="J30" t="s" s="0">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="K30" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L30" s="0">
-        <v>0</v>
-      </c>
-      <c r="M30" s="0">
-        <v>78</v>
-      </c>
-      <c r="N30" s="7">
-        <v>37937</v>
-      </c>
-      <c r="O30" s="7">
-        <v>45355</v>
-      </c>
+      <c r="L30" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <v>46026.0</v>
+      </c>
+      <c r="O30" s="7"/>
       <c r="P30" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>318</v>
       </c>
@@ -3861,31 +3834,29 @@
         <v>254</v>
       </c>
       <c r="I31" t="s" s="0">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J31" t="s" s="0">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="K31" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L31" s="0">
-        <v>0</v>
-      </c>
-      <c r="M31" s="0">
-        <v>71</v>
-      </c>
-      <c r="N31" s="7">
-        <v>43242</v>
-      </c>
-      <c r="O31" s="7">
-        <v>45356</v>
-      </c>
+      <c r="L31" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <v>46027.0</v>
+      </c>
+      <c r="O31" s="7"/>
       <c r="P31" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>325</v>
       </c>
@@ -3908,55 +3879,53 @@
         <v>181</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="I32" t="s" s="0">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="J32" t="s" s="0">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="K32" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L32" s="0">
-        <v>0</v>
-      </c>
-      <c r="M32" s="0">
-        <v>113</v>
-      </c>
-      <c r="N32" s="7">
-        <v>39555</v>
-      </c>
-      <c r="O32" s="7">
-        <v>45357</v>
-      </c>
+      <c r="L32" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="0" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <v>46028.0</v>
+      </c>
+      <c r="O32" s="7"/>
       <c r="P32" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="6"/>
       <c r="G33" s="1"/>
       <c r="H33" s="3"/>
       <c r="O33" s="7"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
       <c r="B34" s="6"/>
       <c r="G34" s="1"/>
       <c r="H34" s="3"/>
       <c r="O34" s="7"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
       <c r="B35" s="6"/>
       <c r="G35" s="1"/>
       <c r="H35" s="3"/>
       <c r="O35" s="7"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>320</v>
       </c>
@@ -3982,31 +3951,29 @@
         <v>255</v>
       </c>
       <c r="I36" t="s" s="0">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="J36" t="s" s="0">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="K36" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L36" s="0">
-        <v>25</v>
-      </c>
-      <c r="M36" s="0">
-        <v>13</v>
-      </c>
-      <c r="N36" s="7">
-        <v>43230</v>
-      </c>
-      <c r="O36" s="7">
-        <v>45361</v>
-      </c>
+      <c r="L36" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <v>43230.0</v>
+      </c>
+      <c r="O36" s="7"/>
       <c r="P36" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>326</v>
       </c>
@@ -4032,31 +3999,29 @@
         <v>256</v>
       </c>
       <c r="I37" t="s" s="0">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="J37" t="s" s="0">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="K37" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L37" s="0">
-        <v>0</v>
-      </c>
-      <c r="M37" s="0">
-        <v>9</v>
-      </c>
-      <c r="N37" s="7">
-        <v>38841</v>
-      </c>
-      <c r="O37" s="7">
-        <v>45362</v>
-      </c>
+      <c r="L37" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="N37" s="7" t="n">
+        <v>38841.0</v>
+      </c>
+      <c r="O37" s="7"/>
       <c r="P37" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>324</v>
       </c>
@@ -4082,31 +4047,29 @@
         <v>257</v>
       </c>
       <c r="I38" t="s" s="0">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J38" t="s" s="0">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="K38" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L38" s="0">
-        <v>0</v>
-      </c>
-      <c r="M38" s="0">
-        <v>120</v>
-      </c>
-      <c r="N38" s="7">
-        <v>44389</v>
-      </c>
-      <c r="O38" s="7">
-        <v>45363</v>
-      </c>
+      <c r="L38" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="N38" s="7" t="n">
+        <v>44389.0</v>
+      </c>
+      <c r="O38" s="7"/>
       <c r="P38" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>320</v>
       </c>
@@ -4132,28 +4095,26 @@
         <v>481</v>
       </c>
       <c r="I39" t="s" s="0">
-        <v>570</v>
+        <v>523</v>
       </c>
       <c r="K39" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L39" s="0">
-        <v>0</v>
-      </c>
-      <c r="M39" s="0">
-        <v>116</v>
-      </c>
-      <c r="N39" s="7">
-        <v>45242</v>
-      </c>
-      <c r="O39" s="7">
-        <v>45364</v>
-      </c>
+      <c r="L39" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="N39" s="7" t="n">
+        <v>45242.0</v>
+      </c>
+      <c r="O39" s="7"/>
       <c r="P39" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>327</v>
       </c>
@@ -4179,31 +4140,29 @@
         <v>258</v>
       </c>
       <c r="I40" t="s" s="0">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="J40" t="s" s="0">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="K40" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L40" s="0">
-        <v>0</v>
-      </c>
-      <c r="M40" s="0">
-        <v>172</v>
-      </c>
-      <c r="N40" s="7">
-        <v>41309</v>
-      </c>
-      <c r="O40" s="7">
-        <v>45365</v>
-      </c>
+      <c r="L40" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>172.0</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <v>41309.0</v>
+      </c>
+      <c r="O40" s="7"/>
       <c r="P40" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>327</v>
       </c>
@@ -4229,31 +4188,29 @@
         <v>259</v>
       </c>
       <c r="I41" t="s" s="0">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="J41" t="s" s="0">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="K41" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L41" s="0">
-        <v>0</v>
-      </c>
-      <c r="M41" s="0">
-        <v>79</v>
-      </c>
-      <c r="N41" s="7">
-        <v>45142</v>
-      </c>
-      <c r="O41" s="7">
-        <v>45366</v>
-      </c>
+      <c r="L41" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="N41" s="7" t="n">
+        <v>45142.0</v>
+      </c>
+      <c r="O41" s="7"/>
       <c r="P41" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>327</v>
       </c>
@@ -4290,14 +4247,12 @@
       <c r="N42" s="7">
         <v>45048</v>
       </c>
-      <c r="O42" s="7">
-        <v>45367</v>
-      </c>
+      <c r="O42" s="7"/>
       <c r="P42" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>328</v>
       </c>
@@ -4323,31 +4278,29 @@
         <v>260</v>
       </c>
       <c r="I43" t="s" s="0">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="J43" t="s" s="0">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="K43" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L43" s="0">
-        <v>0</v>
-      </c>
-      <c r="M43" s="0">
-        <v>154</v>
-      </c>
-      <c r="N43" s="7">
-        <v>44479</v>
-      </c>
-      <c r="O43" s="7">
-        <v>45368</v>
-      </c>
+      <c r="L43" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>154.0</v>
+      </c>
+      <c r="N43" s="7" t="n">
+        <v>44479.0</v>
+      </c>
+      <c r="O43" s="7"/>
       <c r="P43" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>329</v>
       </c>
@@ -4373,31 +4326,29 @@
         <v>261</v>
       </c>
       <c r="I44" t="s" s="0">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="J44" t="s" s="0">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="K44" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L44" s="0">
-        <v>0</v>
-      </c>
-      <c r="M44" s="0">
-        <v>57</v>
-      </c>
-      <c r="N44" s="7">
-        <v>42624</v>
-      </c>
-      <c r="O44" s="7">
-        <v>45369</v>
-      </c>
+      <c r="L44" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <v>42624.0</v>
+      </c>
+      <c r="O44" s="7"/>
       <c r="P44" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>330</v>
       </c>
@@ -4423,31 +4374,29 @@
         <v>262</v>
       </c>
       <c r="I45" t="s" s="0">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="J45" t="s" s="0">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K45" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L45" s="0">
-        <v>0</v>
-      </c>
-      <c r="M45" s="0">
-        <v>99</v>
-      </c>
-      <c r="N45" s="7">
-        <v>42708</v>
-      </c>
-      <c r="O45" s="7">
-        <v>45370</v>
-      </c>
+      <c r="L45" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <v>42708.0</v>
+      </c>
+      <c r="O45" s="7"/>
       <c r="P45" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>331</v>
       </c>
@@ -4473,31 +4422,29 @@
         <v>482</v>
       </c>
       <c r="I46" t="s" s="0">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="J46" t="s" s="0">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="K46" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L46" s="0">
-        <v>0</v>
-      </c>
-      <c r="M46" s="0">
-        <v>65</v>
-      </c>
-      <c r="N46" s="7">
-        <v>44180</v>
-      </c>
-      <c r="O46" s="7">
-        <v>45371</v>
-      </c>
+      <c r="L46" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <v>44180.0</v>
+      </c>
+      <c r="O46" s="7"/>
       <c r="P46" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>332</v>
       </c>
@@ -4534,14 +4481,12 @@
       <c r="N47" s="7">
         <v>45047</v>
       </c>
-      <c r="O47" s="7">
-        <v>45372</v>
-      </c>
+      <c r="O47" s="7"/>
       <c r="P47" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>318</v>
       </c>
@@ -4567,31 +4512,29 @@
         <v>250</v>
       </c>
       <c r="I48" t="s" s="0">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="J48" t="s" s="0">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="K48" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L48" s="0">
-        <v>25</v>
-      </c>
-      <c r="M48" s="0">
-        <v>41</v>
-      </c>
-      <c r="N48" s="7">
-        <v>42182</v>
-      </c>
-      <c r="O48" s="7">
-        <v>45373</v>
-      </c>
+      <c r="L48" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="N48" s="7" t="n">
+        <v>42182.0</v>
+      </c>
+      <c r="O48" s="7"/>
       <c r="P48" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>333</v>
       </c>
@@ -4617,31 +4560,29 @@
         <v>263</v>
       </c>
       <c r="I49" t="s" s="0">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="J49" t="s" s="0">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="K49" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L49" s="0">
-        <v>0</v>
-      </c>
-      <c r="M49" s="0">
-        <v>192</v>
-      </c>
-      <c r="N49" s="7">
-        <v>43032</v>
-      </c>
-      <c r="O49" s="7">
-        <v>45374</v>
-      </c>
+      <c r="L49" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>192.0</v>
+      </c>
+      <c r="N49" s="7" t="n">
+        <v>43032.0</v>
+      </c>
+      <c r="O49" s="7"/>
       <c r="P49" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>334</v>
       </c>
@@ -4667,31 +4608,29 @@
         <v>264</v>
       </c>
       <c r="I50" t="s" s="0">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="J50" t="s" s="0">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="K50" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L50" s="0">
-        <v>0</v>
-      </c>
-      <c r="M50" s="0">
-        <v>88</v>
-      </c>
-      <c r="N50" s="7">
-        <v>42490</v>
-      </c>
-      <c r="O50" s="7">
-        <v>45375</v>
-      </c>
+      <c r="L50" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="N50" s="7" t="n">
+        <v>42490.0</v>
+      </c>
+      <c r="O50" s="7"/>
       <c r="P50" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>335</v>
       </c>
@@ -4717,31 +4656,29 @@
         <v>265</v>
       </c>
       <c r="I51" t="s" s="0">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="J51" t="s" s="0">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="K51" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L51" s="0">
-        <v>25</v>
-      </c>
-      <c r="M51" s="0">
-        <v>157</v>
-      </c>
-      <c r="N51" s="7">
-        <v>39101</v>
-      </c>
-      <c r="O51" s="7">
-        <v>45376</v>
-      </c>
+      <c r="L51" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>157.0</v>
+      </c>
+      <c r="N51" s="7" t="n">
+        <v>39101.0</v>
+      </c>
+      <c r="O51" s="7"/>
       <c r="P51" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>334</v>
       </c>
@@ -4764,34 +4701,32 @@
         <v>195</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="I52" t="s" s="0">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="J52" t="s" s="0">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="K52" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L52" s="0">
-        <v>0</v>
-      </c>
-      <c r="M52" s="0">
-        <v>126</v>
-      </c>
-      <c r="N52" s="7">
-        <v>44962</v>
-      </c>
-      <c r="O52" s="7">
-        <v>45377</v>
-      </c>
+      <c r="L52" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>126.0</v>
+      </c>
+      <c r="N52" s="7" t="n">
+        <v>44962.0</v>
+      </c>
+      <c r="O52" s="7"/>
       <c r="P52" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>334</v>
       </c>
@@ -4814,34 +4749,32 @@
         <v>196</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="I53" t="s" s="0">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="J53" t="s" s="0">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="K53" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L53" s="0">
-        <v>0</v>
-      </c>
-      <c r="M53" s="0">
-        <v>184</v>
-      </c>
-      <c r="N53" s="7">
-        <v>42148</v>
-      </c>
-      <c r="O53" s="7">
-        <v>45378</v>
-      </c>
+      <c r="L53" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>184.0</v>
+      </c>
+      <c r="N53" s="7" t="n">
+        <v>42148.0</v>
+      </c>
+      <c r="O53" s="7"/>
       <c r="P53" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>336</v>
       </c>
@@ -4866,9 +4799,6 @@
       <c r="H54" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="I54" t="s" s="0">
-        <v>597</v>
-      </c>
       <c r="K54" t="s" s="0">
         <v>241</v>
       </c>
@@ -4881,14 +4811,12 @@
       <c r="N54" s="7">
         <v>43805</v>
       </c>
-      <c r="O54" s="7">
-        <v>45379</v>
-      </c>
+      <c r="O54" s="7"/>
       <c r="P54" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>336</v>
       </c>
@@ -4911,58 +4839,56 @@
         <v>198</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="I55" t="s" s="0">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="J55" t="s" s="0">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="K55" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L55" s="0">
-        <v>0</v>
-      </c>
-      <c r="M55" s="0">
-        <v>44</v>
-      </c>
-      <c r="N55" s="7">
-        <v>40575</v>
-      </c>
-      <c r="O55" s="7">
-        <v>45380</v>
-      </c>
+      <c r="L55" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="N55" s="7" t="n">
+        <v>40575.0</v>
+      </c>
+      <c r="O55" s="7"/>
       <c r="P55" s="1" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="6"/>
       <c r="G56" s="1"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="6"/>
       <c r="G57" s="1"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" s="4"/>
       <c r="B58" s="6"/>
       <c r="G58" s="1"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
       <c r="B59" s="6"/>
       <c r="G59" s="1"/>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>337</v>
       </c>
@@ -4985,34 +4911,32 @@
         <v>199</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="I60" t="s" s="0">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="J60" t="s" s="0">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="K60" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L60" s="0">
-        <v>0</v>
-      </c>
-      <c r="M60" s="0">
-        <v>27</v>
-      </c>
-      <c r="N60" s="7">
-        <v>38607</v>
-      </c>
-      <c r="O60" s="7">
-        <v>44927</v>
-      </c>
+      <c r="L60" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M60" s="0" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="N60" s="7" t="n">
+        <v>46055.0</v>
+      </c>
+      <c r="O60" s="7"/>
       <c r="P60" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>316</v>
       </c>
@@ -5038,31 +4962,29 @@
         <v>267</v>
       </c>
       <c r="I61" t="s" s="0">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="J61" t="s" s="0">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="K61" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L61" s="0">
-        <v>0</v>
-      </c>
-      <c r="M61" s="0">
-        <v>167</v>
-      </c>
-      <c r="N61" s="7">
-        <v>42083</v>
-      </c>
-      <c r="O61" s="7">
-        <v>44928</v>
-      </c>
+      <c r="L61" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M61" s="0" t="n">
+        <v>167.0</v>
+      </c>
+      <c r="N61" s="7" t="n">
+        <v>46056.0</v>
+      </c>
+      <c r="O61" s="7"/>
       <c r="P61" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>333</v>
       </c>
@@ -5085,34 +5007,32 @@
         <v>201</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="I62" t="s" s="0">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="J62" t="s" s="0">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="K62" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L62" s="0">
-        <v>25</v>
-      </c>
-      <c r="M62" s="0">
-        <v>82</v>
-      </c>
-      <c r="N62" s="7">
-        <v>39105</v>
-      </c>
-      <c r="O62" s="7">
-        <v>44929</v>
-      </c>
+      <c r="L62" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M62" s="0" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="N62" s="7" t="n">
+        <v>46057.0</v>
+      </c>
+      <c r="O62" s="7"/>
       <c r="P62" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>323</v>
       </c>
@@ -5138,31 +5058,29 @@
         <v>268</v>
       </c>
       <c r="I63" t="s" s="0">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="J63" t="s" s="0">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="K63" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L63" s="0">
-        <v>0</v>
-      </c>
-      <c r="M63" s="0">
-        <v>122</v>
-      </c>
-      <c r="N63" s="7">
-        <v>41938</v>
-      </c>
-      <c r="O63" s="7">
-        <v>44930</v>
-      </c>
+      <c r="L63" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M63" s="0" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="N63" s="7" t="n">
+        <v>46058.0</v>
+      </c>
+      <c r="O63" s="7"/>
       <c r="P63" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>334</v>
       </c>
@@ -5185,31 +5103,29 @@
         <v>269</v>
       </c>
       <c r="I64" t="s" s="0">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="J64" t="s" s="0">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="K64" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L64" s="0">
-        <v>0</v>
-      </c>
-      <c r="M64" s="0">
-        <v>92</v>
-      </c>
-      <c r="N64" s="7">
-        <v>43691</v>
-      </c>
-      <c r="O64" s="7">
-        <v>44931</v>
-      </c>
+      <c r="L64" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M64" s="0" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="N64" s="7" t="n">
+        <v>46059.0</v>
+      </c>
+      <c r="O64" s="7"/>
       <c r="P64" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>323</v>
       </c>
@@ -5232,31 +5148,29 @@
         <v>270</v>
       </c>
       <c r="I65" t="s" s="0">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J65" t="s" s="0">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K65" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L65" s="0">
-        <v>0</v>
-      </c>
-      <c r="M65" s="0">
-        <v>28</v>
-      </c>
-      <c r="N65" s="7">
-        <v>42810</v>
-      </c>
-      <c r="O65" s="7">
-        <v>44932</v>
-      </c>
+      <c r="L65" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M65" s="0" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="N65" s="7" t="n">
+        <v>46060.0</v>
+      </c>
+      <c r="O65" s="7"/>
       <c r="P65" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>338</v>
       </c>
@@ -5276,34 +5190,32 @@
         <v>205</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="I66" t="s" s="0">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="J66" t="s" s="0">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="K66" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L66" s="0">
-        <v>0</v>
-      </c>
-      <c r="M66" s="0">
-        <v>6</v>
-      </c>
-      <c r="N66" s="7">
-        <v>45570</v>
-      </c>
-      <c r="O66" s="7">
-        <v>44933</v>
-      </c>
+      <c r="L66" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M66" s="0" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="N66" s="7" t="n">
+        <v>46061.0</v>
+      </c>
+      <c r="O66" s="7"/>
       <c r="P66" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>335</v>
       </c>
@@ -5329,28 +5241,26 @@
         <v>271</v>
       </c>
       <c r="I67" t="s" s="0">
-        <v>618</v>
+        <v>523</v>
       </c>
       <c r="K67" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L67" s="0">
-        <v>0</v>
-      </c>
-      <c r="M67" s="0">
-        <v>200</v>
-      </c>
-      <c r="N67" s="7">
-        <v>40799</v>
-      </c>
-      <c r="O67" s="7">
-        <v>44934</v>
-      </c>
+      <c r="L67" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M67" s="0" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="N67" s="7" t="n">
+        <v>46062.0</v>
+      </c>
+      <c r="O67" s="7"/>
       <c r="P67" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>335</v>
       </c>
@@ -5376,31 +5286,29 @@
         <v>272</v>
       </c>
       <c r="I68" t="s" s="0">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="J68" t="s" s="0">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="K68" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L68" s="0">
-        <v>0</v>
-      </c>
-      <c r="M68" s="0">
-        <v>23</v>
-      </c>
-      <c r="N68" s="7">
-        <v>42926</v>
-      </c>
-      <c r="O68" s="7">
-        <v>44935</v>
-      </c>
+      <c r="L68" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M68" s="0" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="N68" s="7" t="n">
+        <v>46063.0</v>
+      </c>
+      <c r="O68" s="7"/>
       <c r="P68" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>320</v>
       </c>
@@ -5426,31 +5334,29 @@
         <v>273</v>
       </c>
       <c r="I69" t="s" s="0">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="J69" t="s" s="0">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="K69" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L69" s="0">
-        <v>25</v>
-      </c>
-      <c r="M69" s="0">
-        <v>183</v>
-      </c>
-      <c r="N69" s="7">
-        <v>43569</v>
-      </c>
-      <c r="O69" s="7">
-        <v>44936</v>
-      </c>
+      <c r="L69" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M69" s="0" t="n">
+        <v>183.0</v>
+      </c>
+      <c r="N69" s="7" t="n">
+        <v>46064.0</v>
+      </c>
+      <c r="O69" s="7"/>
       <c r="P69" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>339</v>
       </c>
@@ -5476,28 +5382,26 @@
         <v>485</v>
       </c>
       <c r="I70" t="s" s="0">
-        <v>623</v>
+        <v>523</v>
       </c>
       <c r="K70" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L70" s="0">
-        <v>0</v>
-      </c>
-      <c r="M70" s="0">
-        <v>73</v>
-      </c>
-      <c r="N70" s="7">
-        <v>42657</v>
-      </c>
-      <c r="O70" s="7">
-        <v>44937</v>
-      </c>
+      <c r="L70" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="N70" s="7" t="n">
+        <v>42657.0</v>
+      </c>
+      <c r="O70" s="7"/>
       <c r="P70" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>338</v>
       </c>
@@ -5520,34 +5424,32 @@
         <v>209</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="I71" t="s" s="0">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="J71" t="s" s="0">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="K71" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L71" s="0">
-        <v>0</v>
-      </c>
-      <c r="M71" s="0">
-        <v>180</v>
-      </c>
-      <c r="N71" s="7">
-        <v>38841</v>
-      </c>
-      <c r="O71" s="7">
-        <v>44938</v>
-      </c>
+      <c r="L71" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M71" s="0" t="n">
+        <v>180.0</v>
+      </c>
+      <c r="N71" s="7" t="n">
+        <v>38841.0</v>
+      </c>
+      <c r="O71" s="7"/>
       <c r="P71" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>334</v>
       </c>
@@ -5573,31 +5475,29 @@
         <v>274</v>
       </c>
       <c r="I72" t="s" s="0">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="J72" t="s" s="0">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="K72" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L72" s="0">
-        <v>0</v>
-      </c>
-      <c r="M72" s="0">
-        <v>187</v>
-      </c>
-      <c r="N72" s="7">
-        <v>42522</v>
-      </c>
-      <c r="O72" s="7">
-        <v>44939</v>
-      </c>
+      <c r="L72" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M72" s="0" t="n">
+        <v>187.0</v>
+      </c>
+      <c r="N72" s="7" t="n">
+        <v>42522.0</v>
+      </c>
+      <c r="O72" s="7"/>
       <c r="P72" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>339</v>
       </c>
@@ -5620,34 +5520,32 @@
         <v>211</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="I73" t="s" s="0">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="J73" t="s" s="0">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="K73" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L73" s="0">
-        <v>0</v>
-      </c>
-      <c r="M73" s="0">
-        <v>18</v>
-      </c>
-      <c r="N73" s="7">
-        <v>39748</v>
-      </c>
-      <c r="O73" s="7">
-        <v>44940</v>
-      </c>
+      <c r="L73" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M73" s="0" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="N73" s="7" t="n">
+        <v>39748.0</v>
+      </c>
+      <c r="O73" s="7"/>
       <c r="P73" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>315</v>
       </c>
@@ -5673,31 +5571,29 @@
         <v>275</v>
       </c>
       <c r="I74" t="s" s="0">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="J74" t="s" s="0">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="K74" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L74" s="0">
-        <v>25</v>
-      </c>
-      <c r="M74" s="0">
-        <v>109</v>
-      </c>
-      <c r="N74" s="7">
-        <v>40427</v>
-      </c>
-      <c r="O74" s="7">
-        <v>44941</v>
-      </c>
+      <c r="L74" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M74" s="0" t="n">
+        <v>109.0</v>
+      </c>
+      <c r="N74" s="7" t="n">
+        <v>40427.0</v>
+      </c>
+      <c r="O74" s="7"/>
       <c r="P74" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>335</v>
       </c>
@@ -5720,34 +5616,32 @@
         <v>213</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="I75" t="s" s="0">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="J75" t="s" s="0">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="K75" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L75" s="0">
-        <v>0</v>
-      </c>
-      <c r="M75" s="0">
-        <v>12</v>
-      </c>
-      <c r="N75" s="7">
-        <v>42543</v>
-      </c>
-      <c r="O75" s="7">
-        <v>44942</v>
-      </c>
+      <c r="L75" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M75" s="0" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="N75" s="7" t="n">
+        <v>42543.0</v>
+      </c>
+      <c r="O75" s="7"/>
       <c r="P75" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>338</v>
       </c>
@@ -5773,28 +5667,26 @@
         <v>276</v>
       </c>
       <c r="I76" t="s" s="0">
-        <v>637</v>
+        <v>523</v>
       </c>
       <c r="K76" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L76" s="0">
-        <v>0</v>
-      </c>
-      <c r="M76" s="0">
-        <v>174</v>
-      </c>
-      <c r="N76" s="7">
-        <v>45341</v>
-      </c>
-      <c r="O76" s="7">
-        <v>45674</v>
-      </c>
+      <c r="L76" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M76" s="0" t="n">
+        <v>174.0</v>
+      </c>
+      <c r="N76" s="7" t="n">
+        <v>45341.0</v>
+      </c>
+      <c r="O76" s="7"/>
       <c r="P76" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>338</v>
       </c>
@@ -5817,37 +5709,35 @@
         <v>214</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="I77" t="s" s="0">
-        <v>639</v>
+        <v>523</v>
       </c>
       <c r="K77" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L77" s="0">
-        <v>0</v>
-      </c>
-      <c r="M77" s="0">
-        <v>112</v>
-      </c>
-      <c r="N77" s="7">
-        <v>39295</v>
-      </c>
-      <c r="O77" s="7">
-        <v>44944</v>
-      </c>
+      <c r="L77" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M77" s="0" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="N77" s="7" t="n">
+        <v>39295.0</v>
+      </c>
+      <c r="O77" s="7"/>
       <c r="P77" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="6"/>
       <c r="G78" s="1"/>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>335</v>
       </c>
@@ -5870,34 +5760,32 @@
         <v>215</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="I79" t="s" s="0">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="J79" t="s" s="0">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="K79" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L79" s="0">
-        <v>0</v>
-      </c>
-      <c r="M79" s="0">
-        <v>121</v>
-      </c>
-      <c r="N79" s="7">
-        <v>45483</v>
-      </c>
-      <c r="O79" s="7">
-        <v>44562</v>
-      </c>
+      <c r="L79" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M79" s="0" t="n">
+        <v>121.0</v>
+      </c>
+      <c r="N79" s="7" t="n">
+        <v>45483.0</v>
+      </c>
+      <c r="O79" s="7"/>
       <c r="P79" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>335</v>
       </c>
@@ -5920,34 +5808,32 @@
         <v>216</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="I80" t="s" s="0">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="J80" t="s" s="0">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="K80" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L80" s="0">
-        <v>25</v>
-      </c>
-      <c r="M80" s="0">
-        <v>146</v>
-      </c>
-      <c r="N80" s="7">
-        <v>45484</v>
-      </c>
-      <c r="O80" s="7">
-        <v>44563</v>
-      </c>
+      <c r="L80" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M80" s="0" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="N80" s="7" t="n">
+        <v>45484.0</v>
+      </c>
+      <c r="O80" s="7"/>
       <c r="P80" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>340</v>
       </c>
@@ -5973,31 +5859,29 @@
         <v>277</v>
       </c>
       <c r="I81" t="s" s="0">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="J81" t="s" s="0">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="K81" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L81" s="0">
-        <v>0</v>
-      </c>
-      <c r="M81" s="0">
-        <v>139</v>
-      </c>
-      <c r="N81" s="7">
-        <v>45485</v>
-      </c>
-      <c r="O81" s="7">
-        <v>44564</v>
-      </c>
+      <c r="L81" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M81" s="0" t="n">
+        <v>139.0</v>
+      </c>
+      <c r="N81" s="7" t="n">
+        <v>45485.0</v>
+      </c>
+      <c r="O81" s="7"/>
       <c r="P81" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>341</v>
       </c>
@@ -6020,34 +5904,32 @@
         <v>218</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="I82" t="s" s="0">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="J82" t="s" s="0">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="K82" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L82" s="0">
-        <v>0</v>
-      </c>
-      <c r="M82" s="0">
-        <v>6</v>
-      </c>
-      <c r="N82" s="7">
-        <v>45486</v>
-      </c>
-      <c r="O82" s="7">
-        <v>44565</v>
-      </c>
+      <c r="L82" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M82" s="0" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="N82" s="7" t="n">
+        <v>45486.0</v>
+      </c>
+      <c r="O82" s="7"/>
       <c r="P82" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>339</v>
       </c>
@@ -6070,31 +5952,29 @@
         <v>219</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="I83" t="s" s="0">
-        <v>652</v>
+        <v>523</v>
       </c>
       <c r="K83" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L83" s="0">
-        <v>0</v>
-      </c>
-      <c r="M83" s="0">
-        <v>63</v>
-      </c>
-      <c r="N83" s="7">
-        <v>45487</v>
-      </c>
-      <c r="O83" s="7">
-        <v>44566</v>
-      </c>
+      <c r="L83" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M83" s="0" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="N83" s="7" t="n">
+        <v>45487.0</v>
+      </c>
+      <c r="O83" s="7"/>
       <c r="P83" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>342</v>
       </c>
@@ -6117,38 +5997,36 @@
         <v>278</v>
       </c>
       <c r="I84" t="s" s="0">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="J84" t="s" s="0">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="K84" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L84" s="0">
-        <v>0</v>
-      </c>
-      <c r="M84" s="0">
-        <v>123</v>
-      </c>
-      <c r="N84" s="7">
-        <v>45488</v>
-      </c>
-      <c r="O84" s="7">
-        <v>44567</v>
-      </c>
+      <c r="L84" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M84" s="0" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="N84" s="7" t="n">
+        <v>45488.0</v>
+      </c>
+      <c r="O84" s="7"/>
       <c r="P84" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="6"/>
       <c r="G85" s="1"/>
       <c r="H85" s="3"/>
       <c r="O85" s="7"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>344</v>
       </c>
@@ -6174,31 +6052,29 @@
         <v>279</v>
       </c>
       <c r="I86" t="s" s="0">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="J86" t="s" s="0">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="K86" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L86" s="0">
-        <v>25</v>
-      </c>
-      <c r="M86" s="0">
-        <v>170</v>
-      </c>
-      <c r="N86" s="7">
-        <v>45490</v>
-      </c>
-      <c r="O86" s="7">
-        <v>44569</v>
-      </c>
+      <c r="L86" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M86" s="0" t="n">
+        <v>170.0</v>
+      </c>
+      <c r="N86" s="7" t="n">
+        <v>45490.0</v>
+      </c>
+      <c r="O86" s="7"/>
       <c r="P86" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>344</v>
       </c>
@@ -6224,31 +6100,29 @@
         <v>280</v>
       </c>
       <c r="I87" t="s" s="0">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="J87" t="s" s="0">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="K87" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L87" s="0">
-        <v>0</v>
-      </c>
-      <c r="M87" s="0">
-        <v>171</v>
-      </c>
-      <c r="N87" s="7">
-        <v>45491</v>
-      </c>
-      <c r="O87" s="7">
-        <v>44570</v>
-      </c>
+      <c r="L87" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M87" s="0" t="n">
+        <v>171.0</v>
+      </c>
+      <c r="N87" s="7" t="n">
+        <v>45491.0</v>
+      </c>
+      <c r="O87" s="7"/>
       <c r="P87" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>333</v>
       </c>
@@ -6271,34 +6145,32 @@
         <v>223</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="I88" t="s" s="0">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="J88" t="s" s="0">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="K88" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L88" s="0">
-        <v>0</v>
-      </c>
-      <c r="M88" s="0">
-        <v>93</v>
-      </c>
-      <c r="N88" s="7">
-        <v>45492</v>
-      </c>
-      <c r="O88" s="7">
-        <v>44571</v>
-      </c>
+      <c r="L88" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M88" s="0" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="N88" s="7" t="n">
+        <v>45492.0</v>
+      </c>
+      <c r="O88" s="7"/>
       <c r="P88" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>333</v>
       </c>
@@ -6321,34 +6193,32 @@
         <v>224</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="I89" t="s" s="0">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="J89" t="s" s="0">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="K89" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L89" s="0">
-        <v>0</v>
-      </c>
-      <c r="M89" s="0">
-        <v>40</v>
-      </c>
-      <c r="N89" s="7">
-        <v>45493</v>
-      </c>
-      <c r="O89" s="7">
-        <v>44572</v>
-      </c>
+      <c r="L89" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M89" s="0" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="N89" s="7" t="n">
+        <v>45493.0</v>
+      </c>
+      <c r="O89" s="7"/>
       <c r="P89" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>345</v>
       </c>
@@ -6371,28 +6241,26 @@
         <v>281</v>
       </c>
       <c r="I90" t="s" s="0">
-        <v>665</v>
+        <v>523</v>
       </c>
       <c r="K90" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L90" s="0">
-        <v>0</v>
-      </c>
-      <c r="M90" s="0">
-        <v>118</v>
-      </c>
-      <c r="N90" s="7">
-        <v>45494</v>
-      </c>
-      <c r="O90" s="7">
-        <v>44573</v>
-      </c>
+      <c r="L90" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M90" s="0" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="N90" s="7" t="n">
+        <v>45494.0</v>
+      </c>
+      <c r="O90" s="7"/>
       <c r="P90" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>346</v>
       </c>
@@ -6418,31 +6286,29 @@
         <v>282</v>
       </c>
       <c r="I91" t="s" s="0">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="J91" t="s" s="0">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="K91" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L91" s="0">
-        <v>0</v>
-      </c>
-      <c r="M91" s="0">
-        <v>125</v>
-      </c>
-      <c r="N91" s="7">
-        <v>45495</v>
-      </c>
-      <c r="O91" s="7">
-        <v>44574</v>
-      </c>
+      <c r="L91" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M91" s="0" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="N91" s="7" t="n">
+        <v>45495.0</v>
+      </c>
+      <c r="O91" s="7"/>
       <c r="P91" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>347</v>
       </c>
@@ -6465,34 +6331,33 @@
         <v>226</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="I92" t="s" s="0">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="J92" t="s" s="0">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="K92" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L92" s="0">
-        <v>0</v>
-      </c>
-      <c r="M92" s="0">
-        <v>56</v>
-      </c>
-      <c r="N92" s="7">
-        <v>45496</v>
-      </c>
-      <c r="O92" s="7">
-        <v>44575</v>
-      </c>
+      <c r="L92" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M92" s="0" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="N92" s="7" t="n">
+        <v>45496.0</v>
+      </c>
+      <c r="O92" s="7"/>
       <c r="P92" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+      <c r="R92" s="1"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>340</v>
       </c>
@@ -6515,34 +6380,32 @@
         <v>227</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="I93" t="s" s="0">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="J93" t="s" s="0">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="K93" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L93" s="0">
-        <v>25</v>
-      </c>
-      <c r="M93" s="0">
-        <v>88</v>
-      </c>
-      <c r="N93" s="7">
-        <v>45497</v>
-      </c>
-      <c r="O93" s="7">
-        <v>44576</v>
-      </c>
+      <c r="L93" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M93" s="0" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="N93" s="7" t="n">
+        <v>45497.0</v>
+      </c>
+      <c r="O93" s="7"/>
       <c r="P93" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>348</v>
       </c>
@@ -6561,33 +6424,33 @@
       <c r="F94" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="G94" s="1"/>
+      <c r="G94" s="1" t="s">
+        <v>662</v>
+      </c>
       <c r="H94" s="3" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="I94" t="s" s="0">
-        <v>675</v>
+        <v>523</v>
       </c>
       <c r="K94" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L94" s="0">
-        <v>0</v>
-      </c>
-      <c r="M94" s="0">
-        <v>116</v>
-      </c>
-      <c r="N94" s="7">
-        <v>45498</v>
-      </c>
-      <c r="O94" s="7">
-        <v>44577</v>
-      </c>
+      <c r="L94" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M94" s="0" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="N94" s="7" t="n">
+        <v>45498.0</v>
+      </c>
+      <c r="O94" s="7"/>
       <c r="P94" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>349</v>
       </c>
@@ -6613,73 +6476,71 @@
         <v>283</v>
       </c>
       <c r="I95" t="s" s="0">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="J95" t="s" s="0">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="K95" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L95" s="0">
-        <v>0</v>
-      </c>
-      <c r="M95" s="0">
-        <v>31</v>
-      </c>
-      <c r="N95" s="7">
-        <v>45499</v>
-      </c>
-      <c r="O95" s="7">
-        <v>44578</v>
-      </c>
+      <c r="L95" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M95" s="0" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="N95" s="7" t="n">
+        <v>45499.0</v>
+      </c>
+      <c r="O95" s="7"/>
       <c r="P95" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="4"/>
       <c r="B96" s="6"/>
       <c r="G96" s="1"/>
       <c r="H96" s="3"/>
       <c r="O96" s="7"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="6"/>
       <c r="G97" s="1"/>
       <c r="H97" s="3"/>
       <c r="O97" s="7"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="4"/>
       <c r="B98" s="6"/>
       <c r="G98" s="1"/>
       <c r="H98" s="3"/>
       <c r="O98" s="7"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="4"/>
       <c r="B99" s="6"/>
       <c r="G99" s="1"/>
       <c r="H99" s="3"/>
       <c r="O99" s="7"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="4"/>
       <c r="B100" s="6"/>
       <c r="G100" s="1"/>
       <c r="H100" s="3"/>
       <c r="O100" s="7"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="6"/>
       <c r="G101" s="1"/>
       <c r="H101" s="3"/>
       <c r="O101" s="7"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>323</v>
       </c>
@@ -6702,34 +6563,32 @@
         <v>229</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="I102" t="s" s="0">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="J102" t="s" s="0">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="K102" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L102" s="0">
-        <v>0</v>
-      </c>
-      <c r="M102" s="0">
-        <v>17</v>
-      </c>
-      <c r="N102" s="7">
-        <v>45506</v>
-      </c>
-      <c r="O102" s="7">
-        <v>44585</v>
-      </c>
+      <c r="L102" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M102" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="N102" s="7" t="n">
+        <v>45506.0</v>
+      </c>
+      <c r="O102" s="7"/>
       <c r="P102" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>350</v>
       </c>
@@ -6755,31 +6614,29 @@
         <v>471</v>
       </c>
       <c r="I103" t="s" s="0">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="J103" t="s" s="0">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="K103" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L103" s="0">
-        <v>25</v>
-      </c>
-      <c r="M103" s="0">
-        <v>52</v>
-      </c>
-      <c r="N103" s="7">
-        <v>45507</v>
-      </c>
-      <c r="O103" s="7">
-        <v>44586</v>
-      </c>
+      <c r="L103" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M103" s="0" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="N103" s="7" t="n">
+        <v>45507.0</v>
+      </c>
+      <c r="O103" s="7"/>
       <c r="P103" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>351</v>
       </c>
@@ -6805,31 +6662,29 @@
         <v>284</v>
       </c>
       <c r="I104" t="s" s="0">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="J104" t="s" s="0">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="K104" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L104" s="0">
-        <v>0</v>
-      </c>
-      <c r="M104" s="0">
-        <v>135</v>
-      </c>
-      <c r="N104" s="7">
-        <v>45508</v>
-      </c>
-      <c r="O104" s="7">
-        <v>44587</v>
-      </c>
+      <c r="L104" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M104" s="0" t="n">
+        <v>135.0</v>
+      </c>
+      <c r="N104" s="7" t="n">
+        <v>45508.0</v>
+      </c>
+      <c r="O104" s="7"/>
       <c r="P104" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>352</v>
       </c>
@@ -6854,9 +6709,6 @@
       <c r="H105" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I105" t="s" s="0">
-        <v>685</v>
-      </c>
       <c r="K105" t="s" s="0">
         <v>241</v>
       </c>
@@ -6869,14 +6721,12 @@
       <c r="N105" s="7">
         <v>45509</v>
       </c>
-      <c r="O105" s="7">
-        <v>44588</v>
-      </c>
+      <c r="O105" s="7"/>
       <c r="P105" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>352</v>
       </c>
@@ -6899,174 +6749,172 @@
         <v>233</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="I106" t="s" s="0">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="J106" t="s" s="0">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="K106" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L106" s="0">
-        <v>25</v>
-      </c>
-      <c r="M106" s="0">
-        <v>127</v>
-      </c>
-      <c r="N106" s="7">
-        <v>45510</v>
-      </c>
-      <c r="O106" s="7">
-        <v>44589</v>
-      </c>
+      <c r="L106" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M106" s="0" t="n">
+        <v>127.0</v>
+      </c>
+      <c r="N106" s="7" t="n">
+        <v>45510.0</v>
+      </c>
+      <c r="O106" s="7"/>
       <c r="P106" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="6"/>
       <c r="G107" s="1"/>
       <c r="H107" s="3"/>
       <c r="O107" s="7"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="6"/>
       <c r="G108" s="1"/>
       <c r="H108" s="3"/>
       <c r="O108" s="7"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="6"/>
       <c r="G109" s="1"/>
       <c r="H109" s="3"/>
       <c r="O109" s="7"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="6"/>
       <c r="G110" s="1"/>
       <c r="H110" s="3"/>
       <c r="O110" s="7"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="6"/>
       <c r="G111" s="1"/>
       <c r="H111" s="3"/>
       <c r="O111" s="7"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="6"/>
       <c r="G112" s="1"/>
       <c r="H112" s="3"/>
       <c r="O112" s="7"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="6"/>
       <c r="G113" s="1"/>
       <c r="H113" s="3"/>
       <c r="O113" s="7"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="6"/>
       <c r="G114" s="1"/>
       <c r="H114" s="3"/>
       <c r="O114" s="7"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="6"/>
       <c r="G115" s="1"/>
       <c r="H115" s="3"/>
       <c r="O115" s="7"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="6"/>
       <c r="G116" s="1"/>
       <c r="H116" s="3"/>
       <c r="O116" s="7"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="6"/>
       <c r="G117" s="1"/>
       <c r="H117" s="3"/>
       <c r="O117" s="7"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="6"/>
       <c r="G118" s="1"/>
       <c r="H118" s="3"/>
       <c r="O118" s="7"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="6"/>
       <c r="G119" s="1"/>
       <c r="H119" s="3"/>
       <c r="O119" s="7"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="6"/>
       <c r="G120" s="1"/>
       <c r="H120" s="3"/>
       <c r="O120" s="7"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="6"/>
       <c r="G121" s="1"/>
       <c r="H121" s="3"/>
       <c r="O121" s="7"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="6"/>
       <c r="G122" s="1"/>
       <c r="H122" s="3"/>
       <c r="O122" s="7"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="6"/>
       <c r="G123" s="1"/>
       <c r="H123" s="3"/>
       <c r="O123" s="7"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="6"/>
       <c r="G124" s="1"/>
       <c r="H124" s="3"/>
       <c r="O124" s="7"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="6"/>
       <c r="G125" s="1"/>
       <c r="H125" s="3"/>
       <c r="O125" s="7"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="6"/>
       <c r="G126" s="1"/>
       <c r="H126" s="3"/>
       <c r="O126" s="7"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>353</v>
       </c>
@@ -7092,28 +6940,26 @@
         <v>286</v>
       </c>
       <c r="I127" t="s" s="0">
-        <v>689</v>
+        <v>523</v>
       </c>
       <c r="K127" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L127" s="0">
-        <v>0</v>
-      </c>
-      <c r="M127" s="0">
-        <v>95</v>
-      </c>
-      <c r="N127" s="7">
-        <v>45531</v>
-      </c>
-      <c r="O127" s="7">
-        <v>45706</v>
-      </c>
+      <c r="L127" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M127" s="0" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="N127" s="7" t="n">
+        <v>45531.0</v>
+      </c>
+      <c r="O127" s="7"/>
       <c r="P127" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>343</v>
       </c>
@@ -7139,31 +6985,29 @@
         <v>472</v>
       </c>
       <c r="I128" t="s" s="0">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="J128" t="s" s="0">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="K128" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L128" s="0">
-        <v>0</v>
-      </c>
-      <c r="M128" s="0">
-        <v>195</v>
-      </c>
-      <c r="N128" s="7">
-        <v>45532</v>
-      </c>
-      <c r="O128" s="7">
-        <v>44611</v>
-      </c>
+      <c r="L128" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M128" s="0" t="n">
+        <v>195.0</v>
+      </c>
+      <c r="N128" s="7" t="n">
+        <v>45532.0</v>
+      </c>
+      <c r="O128" s="7"/>
       <c r="P128" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>343</v>
       </c>
@@ -7186,34 +7030,32 @@
         <v>235</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="I129" t="s" s="0">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="J129" t="s" s="0">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="K129" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L129" s="0">
-        <v>0</v>
-      </c>
-      <c r="M129" s="0">
-        <v>117</v>
-      </c>
-      <c r="N129" s="7">
-        <v>45533</v>
-      </c>
-      <c r="O129" s="7">
-        <v>44612</v>
-      </c>
+      <c r="L129" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M129" s="0" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="N129" s="7" t="n">
+        <v>45533.0</v>
+      </c>
+      <c r="O129" s="7"/>
       <c r="P129" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>353</v>
       </c>
@@ -7239,28 +7081,26 @@
         <v>287</v>
       </c>
       <c r="I130" t="s" s="0">
-        <v>695</v>
+        <v>523</v>
       </c>
       <c r="K130" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L130" s="0">
-        <v>25</v>
-      </c>
-      <c r="M130" s="0">
-        <v>36</v>
-      </c>
-      <c r="N130" s="7">
-        <v>45534</v>
-      </c>
-      <c r="O130" s="7">
-        <v>44613</v>
-      </c>
+      <c r="L130" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M130" s="0" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="N130" s="7" t="n">
+        <v>45534.0</v>
+      </c>
+      <c r="O130" s="7"/>
       <c r="P130" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>343</v>
       </c>
@@ -7286,31 +7126,29 @@
         <v>288</v>
       </c>
       <c r="I131" t="s" s="0">
-        <v>696</v>
+        <v>681</v>
       </c>
       <c r="J131" t="s" s="0">
-        <v>697</v>
+        <v>682</v>
       </c>
       <c r="K131" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L131" s="0">
-        <v>0</v>
-      </c>
-      <c r="M131" s="0">
-        <v>54</v>
-      </c>
-      <c r="N131" s="7">
-        <v>45535</v>
-      </c>
-      <c r="O131" s="7">
-        <v>44614</v>
-      </c>
+      <c r="L131" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M131" s="0" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="N131" s="7" t="n">
+        <v>45535.0</v>
+      </c>
+      <c r="O131" s="7"/>
       <c r="P131" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>343</v>
       </c>
@@ -7336,31 +7174,29 @@
         <v>289</v>
       </c>
       <c r="I132" t="s" s="0">
-        <v>698</v>
+        <v>683</v>
       </c>
       <c r="J132" t="s" s="0">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="K132" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="L132" s="0">
-        <v>0</v>
-      </c>
-      <c r="M132" s="0">
-        <v>76</v>
-      </c>
-      <c r="N132" s="7">
-        <v>45536</v>
-      </c>
-      <c r="O132" s="7">
-        <v>44615</v>
-      </c>
+      <c r="L132" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M132" s="0" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="N132" s="7" t="n">
+        <v>45536.0</v>
+      </c>
+      <c r="O132" s="7"/>
       <c r="P132" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>354</v>
       </c>
@@ -7386,31 +7222,29 @@
         <v>290</v>
       </c>
       <c r="I133" t="s" s="0">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="J133" t="s" s="0">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="K133" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L133" s="0">
-        <v>0</v>
-      </c>
-      <c r="M133" s="0">
-        <v>67</v>
-      </c>
-      <c r="N133" s="7">
-        <v>45537</v>
-      </c>
-      <c r="O133" s="7">
-        <v>44616</v>
-      </c>
+      <c r="L133" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M133" s="0" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="N133" s="7" t="n">
+        <v>45537.0</v>
+      </c>
+      <c r="O133" s="7"/>
       <c r="P133" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>355</v>
       </c>
@@ -7436,31 +7270,29 @@
         <v>291</v>
       </c>
       <c r="I134" t="s" s="0">
-        <v>702</v>
+        <v>687</v>
       </c>
       <c r="J134" t="s" s="0">
-        <v>703</v>
+        <v>688</v>
       </c>
       <c r="K134" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L134" s="0">
-        <v>25</v>
-      </c>
-      <c r="M134" s="0">
-        <v>110</v>
-      </c>
-      <c r="N134" s="7">
-        <v>45538</v>
-      </c>
-      <c r="O134" s="7">
-        <v>44617</v>
-      </c>
+      <c r="L134" s="0" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="M134" s="0" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="N134" s="7" t="n">
+        <v>45538.0</v>
+      </c>
+      <c r="O134" s="7"/>
       <c r="P134" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>315</v>
       </c>
@@ -7479,33 +7311,33 @@
       <c r="F135" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="G135" s="1"/>
+      <c r="G135" s="1" t="s">
+        <v>662</v>
+      </c>
       <c r="H135" s="3" t="s">
-        <v>704</v>
+        <v>689</v>
       </c>
       <c r="I135" t="s" s="0">
-        <v>705</v>
+        <v>523</v>
       </c>
       <c r="K135" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L135" s="0">
-        <v>0</v>
-      </c>
-      <c r="M135" s="0">
-        <v>160</v>
-      </c>
-      <c r="N135" s="7">
-        <v>45539</v>
-      </c>
-      <c r="O135" s="7">
-        <v>44618</v>
-      </c>
+      <c r="L135" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M135" s="0" t="n">
+        <v>160.0</v>
+      </c>
+      <c r="N135" s="7" t="n">
+        <v>45539.0</v>
+      </c>
+      <c r="O135" s="7"/>
       <c r="P135" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>321</v>
       </c>
@@ -7528,93 +7360,91 @@
         <v>240</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="I136" t="s" s="0">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="J136" t="s" s="0">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="K136" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="L136" s="0">
-        <v>0</v>
-      </c>
-      <c r="M136" s="0">
-        <v>17</v>
-      </c>
-      <c r="N136" s="7">
-        <v>45540</v>
-      </c>
-      <c r="O136" s="7">
-        <v>44619</v>
-      </c>
+      <c r="L136" s="0" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M136" s="0" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="N136" s="7" t="n">
+        <v>45540.0</v>
+      </c>
+      <c r="O136" s="7"/>
       <c r="P136" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="6"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="6"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="6"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="6"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="6"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="6"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="6"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="6"/>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="6"/>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="6"/>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="6"/>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="6"/>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="6"/>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
       <c r="B150" s="6"/>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B151" s="6"/>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B152" s="6"/>
     </row>
   </sheetData>
@@ -7626,16 +7456,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31A8F51-8D2A-4E56-BAC3-F686CC936FAB}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" customWidth="true" width="46.0"/>
-    <col min="5" max="5" customWidth="true" width="15.85546875"/>
-    <col min="6" max="6" customWidth="true" width="14.85546875"/>
-    <col min="7" max="7" customWidth="true" width="14.28515625"/>
-    <col min="11" max="12" customWidth="true" width="20.7109375"/>
+    <col min="5" max="5" customWidth="true" width="15.88671875"/>
+    <col min="6" max="6" customWidth="true" width="14.88671875"/>
+    <col min="7" max="7" customWidth="true" width="14.33203125"/>
+    <col min="11" max="12" customWidth="true" width="20.6640625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s" s="0">
         <v>399</v>
       </c>
@@ -7676,39 +7506,33 @@
         <v>398</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="0">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>407</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>401</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="K2" s="0">
-        <v>10</v>
-      </c>
-      <c r="L2" s="0">
-        <v>2</v>
+        <v>421</v>
+      </c>
+      <c r="H2" s="0">
+        <v>20</v>
       </c>
       <c r="M2" s="0">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="0">
         <v>2</v>
       </c>
@@ -7740,18 +7564,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="0">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C4" t="s" s="0">
         <v>407</v>
       </c>
       <c r="D4" t="s" s="0">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>428</v>
@@ -7762,17 +7586,17 @@
       <c r="G4" t="s" s="0">
         <v>241</v>
       </c>
-      <c r="H4" s="0">
-        <v>20</v>
-      </c>
-      <c r="I4" s="0">
+      <c r="K4" s="0">
+        <v>10</v>
+      </c>
+      <c r="L4" s="0">
+        <v>2</v>
+      </c>
+      <c r="M4" s="0">
         <v>0</v>
       </c>
-      <c r="M4" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="0">
         <v>11</v>
       </c>
@@ -7780,10 +7604,10 @@
         <v>445</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>428</v>
@@ -7794,17 +7618,17 @@
       <c r="G5" t="s" s="0">
         <v>241</v>
       </c>
+      <c r="H5" s="0">
+        <v>20</v>
+      </c>
       <c r="I5" s="0">
-        <v>20</v>
-      </c>
-      <c r="J5" s="0">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="0">
         <v>11</v>
       </c>
@@ -7812,10 +7636,10 @@
         <v>445</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s" s="0">
         <v>428</v>
@@ -7827,16 +7651,16 @@
         <v>241</v>
       </c>
       <c r="I6" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J6" s="0">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="0">
         <v>11</v>
       </c>
@@ -7844,10 +7668,10 @@
         <v>445</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E7" t="s" s="0">
         <v>428</v>
@@ -7862,13 +7686,13 @@
         <v>50</v>
       </c>
       <c r="J7" s="0">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="0">
         <v>11</v>
       </c>
@@ -7876,10 +7700,10 @@
         <v>445</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E8" t="s" s="0">
         <v>428</v>
@@ -7891,16 +7715,16 @@
         <v>241</v>
       </c>
       <c r="I8" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J8" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="0">
         <v>11</v>
       </c>
@@ -7908,10 +7732,10 @@
         <v>445</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E9" t="s" s="0">
         <v>428</v>
@@ -7923,56 +7747,59 @@
         <v>241</v>
       </c>
       <c r="I9" s="0">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="J9" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M9" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="0">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>445</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>423</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>450</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>428</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>401</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="I10" s="0">
+        <v>999</v>
+      </c>
+      <c r="J10" s="0">
+        <v>5</v>
+      </c>
+      <c r="M10" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="0">
         <v>12</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B11" t="s" s="0">
         <v>456</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="C11" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="D10" t="s" s="0">
+      <c r="D11" t="s" s="0">
         <v>412</v>
-      </c>
-      <c r="E10" t="s" s="0">
-        <v>427</v>
-      </c>
-      <c r="F10" t="s" s="0">
-        <v>421</v>
-      </c>
-      <c r="K10" s="0">
-        <v>10</v>
-      </c>
-      <c r="L10" s="0">
-        <v>14</v>
-      </c>
-      <c r="M10" s="0">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="0">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s" s="0">
-        <v>452</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>452</v>
-      </c>
-      <c r="D11" t="s" s="0">
-        <v>453</v>
       </c>
       <c r="E11" t="s" s="0">
         <v>427</v>
@@ -7984,24 +7811,24 @@
         <v>10</v>
       </c>
       <c r="L11" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="M11" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>407</v>
+        <v>452</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>408</v>
+        <v>453</v>
       </c>
       <c r="E12" t="s" s="0">
         <v>427</v>
@@ -8009,20 +7836,17 @@
       <c r="F12" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="G12" t="s" s="0">
-        <v>419</v>
-      </c>
-      <c r="H12" s="0">
-        <v>50</v>
-      </c>
-      <c r="I12" s="0">
+      <c r="K12" s="0">
         <v>10</v>
       </c>
+      <c r="L12" s="0">
+        <v>25</v>
+      </c>
       <c r="M12" s="0">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="0">
         <v>14</v>
       </c>
@@ -8030,10 +7854,10 @@
         <v>445</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="E13" t="s" s="0">
         <v>427</v>
@@ -8044,17 +7868,17 @@
       <c r="G13" t="s" s="0">
         <v>419</v>
       </c>
+      <c r="H13" s="0">
+        <v>50</v>
+      </c>
       <c r="I13" s="0">
-        <v>30</v>
-      </c>
-      <c r="J13" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M13" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="0">
         <v>14</v>
       </c>
@@ -8062,10 +7886,10 @@
         <v>445</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s" s="0">
         <v>427</v>
@@ -8077,16 +7901,16 @@
         <v>419</v>
       </c>
       <c r="I14" s="0">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J14" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="0">
         <v>14</v>
       </c>
@@ -8094,10 +7918,10 @@
         <v>445</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E15" t="s" s="0">
         <v>427</v>
@@ -8109,16 +7933,16 @@
         <v>419</v>
       </c>
       <c r="I15" s="0">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J15" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M15" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="0">
         <v>14</v>
       </c>
@@ -8126,10 +7950,10 @@
         <v>445</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>427</v>
@@ -8144,13 +7968,13 @@
         <v>50</v>
       </c>
       <c r="J16" s="0">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M16" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="0">
         <v>14</v>
       </c>
@@ -8158,10 +7982,10 @@
         <v>445</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E17" t="s" s="0">
         <v>427</v>
@@ -8173,27 +7997,27 @@
         <v>419</v>
       </c>
       <c r="I17" s="0">
-        <v>9999</v>
+        <v>50</v>
       </c>
       <c r="J17" s="0">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M17" s="0">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="0">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="C18" t="s" s="0">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="D18" t="s" s="0">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="E18" t="s" s="0">
         <v>427</v>
@@ -8201,14 +8025,20 @@
       <c r="F18" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="H18" s="0">
+      <c r="G18" t="s" s="0">
+        <v>419</v>
+      </c>
+      <c r="I18" s="0">
+        <v>9999</v>
+      </c>
+      <c r="J18" s="0">
         <v>20</v>
       </c>
       <c r="M18" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="0">
         <v>17</v>
       </c>
@@ -8237,7 +8067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="0">
         <v>16</v>
       </c>
@@ -8272,7 +8102,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="0">
         <v>19</v>
       </c>
@@ -8298,7 +8128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="0">
         <v>18</v>
       </c>

--- a/src/main/resources/SistemasBasura.xlsx
+++ b/src/main/resources/SistemasBasura.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\UNIVERSIDAD\Curso 25-26\Sistemas de Informacion II\practica 3\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>
@@ -1574,12 +1574,595 @@
   </si>
   <si>
     <t>3162456104254692000A</t>
+  </si>
+  <si>
+    <t>31645124453461205100</t>
+  </si>
+  <si>
+    <t>65614874115615445600</t>
+  </si>
+  <si>
+    <t>32569523086220165100</t>
+  </si>
+  <si>
+    <t>MC6436520125638451012515</t>
+  </si>
+  <si>
+    <t>rgo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>21584976912154655485</t>
+  </si>
+  <si>
+    <t>ES9621584976912154655485</t>
+  </si>
+  <si>
+    <t>sdo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GR9420125003305201112544</t>
+  </si>
+  <si>
+    <t>vdo00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>FI5620960043043554600000</t>
+  </si>
+  <si>
+    <t>abp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>21564975263245467900</t>
+  </si>
+  <si>
+    <t>LT2132566221532587754888</t>
+  </si>
+  <si>
+    <t>acp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>00750184350702510003</t>
+  </si>
+  <si>
+    <t>74635623W</t>
+  </si>
+  <si>
+    <t>SM1325894363415485700777</t>
+  </si>
+  <si>
+    <t>lbr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>X8465783N</t>
+  </si>
+  <si>
+    <t>ES0396431245188150005111</t>
+  </si>
+  <si>
+    <t>sbr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>83647564Z</t>
+  </si>
+  <si>
+    <t>25030000194574745400</t>
+  </si>
+  <si>
+    <t>AT7125030000194574745400</t>
+  </si>
+  <si>
+    <t>agr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>83948128Z</t>
+  </si>
+  <si>
+    <t>IT2115953684881254695211</t>
+  </si>
+  <si>
+    <t>dgr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>92736981S</t>
+  </si>
+  <si>
+    <t>20960043033096200013</t>
+  </si>
+  <si>
+    <t>ES6520960043033096200013</t>
+  </si>
+  <si>
+    <t>pgs00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7423455254983263234411</t>
+  </si>
+  <si>
+    <t>mq00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GR4920910936583000000000</t>
+  </si>
+  <si>
+    <t>bv00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0420960043052159000011</t>
+  </si>
+  <si>
+    <t>pp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12669681125112121200</t>
+  </si>
+  <si>
+    <t>DE6912669681125112121200</t>
+  </si>
+  <si>
+    <t>pc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2956187775315550000651</t>
+  </si>
+  <si>
+    <t>gmm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0425516848021156151054</t>
+  </si>
+  <si>
+    <t>cgm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>64578946720051516403</t>
+  </si>
+  <si>
+    <t>ES4534698752714600549403</t>
+  </si>
+  <si>
+    <t>csn00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>25147854E</t>
+  </si>
+  <si>
+    <t>23185484415641685908</t>
+  </si>
+  <si>
+    <t>FR8423185484415641685908</t>
+  </si>
+  <si>
+    <t>gmm01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE5021508149175421346497</t>
+  </si>
+  <si>
+    <t>tcp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE6721346154503164978451</t>
+  </si>
+  <si>
+    <t>ccp00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12345678Z</t>
+  </si>
+  <si>
+    <t>ES7225187786311225455548</t>
+  </si>
+  <si>
+    <t>cap00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2396536214865214585214</t>
+  </si>
+  <si>
+    <t>elr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES6885461325251978750005</t>
+  </si>
+  <si>
+    <t>dlr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>75647586157564758698</t>
+  </si>
+  <si>
+    <t>FI6775647586157564758698</t>
+  </si>
+  <si>
+    <t>har00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES5020960043073071400000</t>
+  </si>
+  <si>
+    <t>spr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7521654587985156484454</t>
+  </si>
+  <si>
+    <t>sas00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES8451651681961210656544</t>
+  </si>
+  <si>
+    <t>bfs00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES4675647586157564758698</t>
+  </si>
+  <si>
+    <t>dfg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>GB9720910936583000000000</t>
+  </si>
+  <si>
+    <t>gmg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>DE9301821135910205540000</t>
+  </si>
+  <si>
+    <t>mlg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES2120960043043075700000</t>
+  </si>
+  <si>
+    <t>iag00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>25635478301002541233</t>
+  </si>
+  <si>
+    <t>SM7825635478301002541233</t>
+  </si>
+  <si>
+    <t>gpg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>32154697155423121012</t>
+  </si>
+  <si>
+    <t>ES8932154697155423121012</t>
+  </si>
+  <si>
+    <t>rgg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20008521588775113327</t>
+  </si>
+  <si>
+    <t>GB5720008521588775113327</t>
+  </si>
+  <si>
+    <t>afg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20960043073000100018</t>
+  </si>
+  <si>
+    <t>12548523445214585218</t>
+  </si>
+  <si>
+    <t>ES0912548523445214585218</t>
+  </si>
+  <si>
+    <t>alm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES1436154231712500312566</t>
+  </si>
+  <si>
+    <t>ad00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES8244875664127231645789</t>
+  </si>
+  <si>
+    <t>lr00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20960031482124800018</t>
+  </si>
+  <si>
+    <t>ES2420960031482124800018</t>
+  </si>
+  <si>
+    <t>lc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES1933218885441445121022</t>
+  </si>
+  <si>
+    <t>afg01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES8462581542713690044508</t>
+  </si>
+  <si>
+    <t>dgg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES0725165151118666365191</t>
+  </si>
+  <si>
+    <t>rog00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20960043023000100021</t>
+  </si>
+  <si>
+    <t>ES6020960043023000100021</t>
+  </si>
+  <si>
+    <t>sog00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>65168874681561561522</t>
+  </si>
+  <si>
+    <t>ES2965168874681561561522</t>
+  </si>
+  <si>
+    <t>vmg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES3220960583831234500000</t>
+  </si>
+  <si>
+    <t>mbg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>21416325801510005527</t>
+  </si>
+  <si>
+    <t>ES7421416325801510005527</t>
+  </si>
+  <si>
+    <t>cbg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12345670Y</t>
+  </si>
+  <si>
+    <t>LU0932628484504115151115</t>
+  </si>
+  <si>
+    <t>msh00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>12345679S</t>
+  </si>
+  <si>
+    <t>20960056143231500032</t>
+  </si>
+  <si>
+    <t>ES6620960056143231500032</t>
+  </si>
+  <si>
+    <t>fdl00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>63516541858944000993</t>
+  </si>
+  <si>
+    <t>ES4063516541858944000993</t>
+  </si>
+  <si>
+    <t>sdm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>23658965294585223213</t>
+  </si>
+  <si>
+    <t>ES2923658965294585223213</t>
+  </si>
+  <si>
+    <t>egm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>FI6132658012367712548745</t>
+  </si>
+  <si>
+    <t>gpm00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>23652365132254222021</t>
+  </si>
+  <si>
+    <t>ES5223652365132254222021</t>
+  </si>
+  <si>
+    <t>eam00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20012541120023365296</t>
+  </si>
+  <si>
+    <t>ES9232584216971684051000</t>
+  </si>
+  <si>
+    <t>mg00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>ES7395485212315484010000</t>
+  </si>
+  <si>
+    <t>jac00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>LT9321856333126985542360</t>
+  </si>
+  <si>
+    <t>bdc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>36245978123245679018</t>
+  </si>
+  <si>
+    <t>ES4836245978123245679018</t>
+  </si>
+  <si>
+    <t>ngc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87635467511625345671</t>
+  </si>
+  <si>
+    <t>ES2987635467511625345671</t>
+  </si>
+  <si>
+    <t>mlc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>SE6832574512085411002255</t>
+  </si>
+  <si>
+    <t>mlc01@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>20960043093468900021</t>
+  </si>
+  <si>
+    <t>ES4820960043093468900021</t>
+  </si>
+  <si>
+    <t>cfc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>84729478014857627845</t>
+  </si>
+  <si>
+    <t>ES7884729478014857627845</t>
+  </si>
+  <si>
+    <t>cgc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>85550564796165145618</t>
+  </si>
+  <si>
+    <t>ES1665165654918886005001</t>
+  </si>
+  <si>
+    <t>ksc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>65645150815168448846</t>
+  </si>
+  <si>
+    <t>AT9465645150815168448846</t>
+  </si>
+  <si>
+    <t>mhc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>IT3526551681807651415636</t>
+  </si>
+  <si>
+    <t>cld00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>HU2399558741836555551120</t>
+  </si>
+  <si>
+    <t>mfd00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>51556584261251000242</t>
+  </si>
+  <si>
+    <t>IE4751556584261251000242</t>
+  </si>
+  <si>
+    <t>gmm02@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619137384957654</t>
+  </si>
+  <si>
+    <t>87457619164384957654</t>
+  </si>
+  <si>
+    <t>LT1687457619164384957654</t>
+  </si>
+  <si>
+    <t>dmc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619177384957657</t>
+  </si>
+  <si>
+    <t>ES9587457619177384957657</t>
+  </si>
+  <si>
+    <t>ebc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619117384957658</t>
+  </si>
+  <si>
+    <t>87457619167384957659</t>
+  </si>
+  <si>
+    <t>ES0687457619167384957659</t>
+  </si>
+  <si>
+    <t>msc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619117384957651</t>
+  </si>
+  <si>
+    <t>ES4787457619117384957651</t>
+  </si>
+  <si>
+    <t>mdc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619197384957653</t>
+  </si>
+  <si>
+    <t>ES7987457619197384957653</t>
+  </si>
+  <si>
+    <t>mfc00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619187384957617</t>
+  </si>
+  <si>
+    <t>ES4687457619187384957617</t>
+  </si>
+  <si>
+    <t>cdd00@tasabasura2026.com</t>
+  </si>
+  <si>
+    <t>87457619177384957619</t>
+  </si>
+  <si>
+    <t>87457619187384957621</t>
+  </si>
+  <si>
+    <t>AT6887457619187384957621</t>
+  </si>
+  <si>
+    <t>hpd00@tasabasura2026.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1950,58 +2533,58 @@
   <dimension ref="A1:R152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="22.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="7"/>
-    <col min="16" max="16" width="11.42578125" style="1"/>
+    <col min="1" max="1" customWidth="true" width="30.140625"/>
+    <col min="2" max="2" customWidth="true" style="5" width="30.140625"/>
+    <col min="8" max="8" customWidth="true" width="22.5703125"/>
+    <col min="13" max="13" customWidth="true" width="14.0"/>
+    <col min="14" max="14" style="7" width="11.42578125"/>
+    <col min="16" max="16" style="1" width="11.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>436</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>234</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -2009,37 +2592,37 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>294</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>397</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>476</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="K2" t="s">
-        <v>232</v>
-      </c>
-      <c r="L2">
+        <v>516</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L2" s="0">
         <v>0</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>251</v>
       </c>
       <c r="N2" s="7">
@@ -2059,31 +2642,31 @@
       <c r="B3" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>133</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>477</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="K3" t="s">
-        <v>232</v>
-      </c>
-      <c r="L3">
+        <v>517</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L3" s="0">
         <v>0</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <v>100</v>
       </c>
       <c r="N3" s="7">
@@ -2101,31 +2684,31 @@
       <c r="B4" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>275</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="0">
         <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>478</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="K4" t="s">
-        <v>232</v>
-      </c>
-      <c r="L4">
+        <v>518</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L4" s="0">
         <v>50</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <v>298</v>
       </c>
       <c r="N4" s="7">
@@ -2145,16 +2728,16 @@
       <c r="B5" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="0">
         <v>77</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="0">
         <v>135</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -2163,13 +2746,13 @@
       <c r="H5" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="0">
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="0">
         <v>308</v>
       </c>
       <c r="N5" s="7">
@@ -2189,16 +2772,16 @@
       <c r="B6" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>277</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="0">
         <v>78</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="0">
         <v>136</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -2207,13 +2790,19 @@
       <c r="H6" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="K6" t="s">
-        <v>232</v>
-      </c>
-      <c r="L6">
+      <c r="I6" t="s" s="0">
+        <v>519</v>
+      </c>
+      <c r="J6" t="s" s="0">
+        <v>520</v>
+      </c>
+      <c r="K6" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L6" s="0">
         <v>25</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="0">
         <v>0</v>
       </c>
       <c r="N6" s="7">
@@ -2233,31 +2822,37 @@
       <c r="B7" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="0">
         <v>137</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>438</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="K7" t="s">
-        <v>232</v>
-      </c>
-      <c r="L7">
+        <v>521</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>522</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>523</v>
+      </c>
+      <c r="K7" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L7" s="0">
         <v>0</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="0">
         <v>298</v>
       </c>
       <c r="N7" s="7">
@@ -2277,16 +2872,16 @@
       <c r="B8" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="0">
         <v>118</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -2295,13 +2890,19 @@
       <c r="H8" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="K8" t="s">
-        <v>232</v>
-      </c>
-      <c r="L8">
+      <c r="I8" t="s" s="0">
+        <v>524</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>525</v>
+      </c>
+      <c r="K8" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L8" s="0">
         <v>25</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="0">
         <v>51</v>
       </c>
       <c r="N8" s="7">
@@ -2321,16 +2922,16 @@
       <c r="B9" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="0">
         <v>138</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -2339,13 +2940,13 @@
       <c r="H9" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="K9" t="s">
-        <v>232</v>
-      </c>
-      <c r="L9">
+      <c r="K9" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L9" s="0">
         <v>0</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="0">
         <v>137</v>
       </c>
       <c r="N9" s="7">
@@ -2365,16 +2966,16 @@
       <c r="B10" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="0">
         <v>139</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -2383,13 +2984,19 @@
       <c r="H10" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="K10" t="s">
-        <v>232</v>
-      </c>
-      <c r="L10">
+      <c r="I10" t="s" s="0">
+        <v>526</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>527</v>
+      </c>
+      <c r="K10" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L10" s="0">
         <v>0</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="0">
         <v>43</v>
       </c>
       <c r="N10" s="7">
@@ -2409,31 +3016,31 @@
       <c r="B11" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="0">
         <v>82</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="0">
         <v>125</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>481</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="K11" t="s">
-        <v>232</v>
-      </c>
-      <c r="L11">
+        <v>528</v>
+      </c>
+      <c r="K11" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L11" s="0">
         <v>25</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="0">
         <v>187</v>
       </c>
       <c r="N11" s="7">
@@ -2453,16 +3060,16 @@
       <c r="B12" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="0">
         <v>140</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -2471,13 +3078,19 @@
       <c r="H12" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="K12" t="s">
-        <v>232</v>
-      </c>
-      <c r="L12">
+      <c r="I12" t="s" s="0">
+        <v>529</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>530</v>
+      </c>
+      <c r="K12" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L12" s="0">
         <v>0</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="0">
         <v>0</v>
       </c>
       <c r="N12" s="7">
@@ -2495,16 +3108,16 @@
       <c r="B13" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="0">
         <v>281</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="0">
         <v>109</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -2513,13 +3126,13 @@
       <c r="H13" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="K13" t="s">
-        <v>232</v>
-      </c>
-      <c r="L13">
+      <c r="K13" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L13" s="0">
         <v>0</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="0">
         <v>179</v>
       </c>
       <c r="N13" s="7">
@@ -2539,31 +3152,31 @@
       <c r="B14" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="0">
         <v>282</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="0">
         <v>109</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>410</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="K14" t="s">
-        <v>232</v>
-      </c>
-      <c r="L14">
+        <v>531</v>
+      </c>
+      <c r="K14" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L14" s="0">
         <v>25</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="0">
         <v>48</v>
       </c>
       <c r="N14" s="7">
@@ -2587,31 +3200,37 @@
       <c r="B16" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="0">
         <v>141</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>482</v>
+        <v>532</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="K16" t="s">
-        <v>232</v>
-      </c>
-      <c r="L16">
+      <c r="I16" t="s" s="0">
+        <v>533</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>534</v>
+      </c>
+      <c r="K16" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L16" s="0">
         <v>0</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="0">
         <v>140</v>
       </c>
       <c r="N16" s="7">
@@ -2629,31 +3248,37 @@
       <c r="B17" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="0">
         <v>86</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="0">
         <v>141</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="K17" t="s">
-        <v>232</v>
-      </c>
-      <c r="L17">
+      <c r="I17" t="s" s="0">
+        <v>536</v>
+      </c>
+      <c r="J17" t="s" s="0">
+        <v>537</v>
+      </c>
+      <c r="K17" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L17" s="0">
         <v>0</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="0">
         <v>83</v>
       </c>
       <c r="N17" s="7">
@@ -2671,31 +3296,37 @@
       <c r="B18" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="0">
         <v>142</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>484</v>
+        <v>538</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="K18" t="s">
-        <v>232</v>
-      </c>
-      <c r="L18">
+        <v>539</v>
+      </c>
+      <c r="I18" t="s" s="0">
+        <v>540</v>
+      </c>
+      <c r="J18" t="s" s="0">
+        <v>541</v>
+      </c>
+      <c r="K18" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L18" s="0">
         <v>0</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="0">
         <v>122</v>
       </c>
       <c r="N18" s="7">
@@ -2713,31 +3344,37 @@
       <c r="B19" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="0">
         <v>285</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" t="s" s="0">
         <v>142</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>485</v>
+        <v>542</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="K19" t="s">
-        <v>232</v>
-      </c>
-      <c r="L19">
+      <c r="I19" t="s" s="0">
+        <v>543</v>
+      </c>
+      <c r="J19" t="s" s="0">
+        <v>544</v>
+      </c>
+      <c r="K19" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L19" s="0">
         <v>25</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="0">
         <v>153</v>
       </c>
       <c r="N19" s="7">
@@ -2755,31 +3392,37 @@
       <c r="B20" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="0">
         <v>143</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>486</v>
+        <v>545</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="K20" t="s">
-        <v>232</v>
-      </c>
-      <c r="L20">
+        <v>546</v>
+      </c>
+      <c r="I20" t="s" s="0">
+        <v>547</v>
+      </c>
+      <c r="J20" t="s" s="0">
+        <v>548</v>
+      </c>
+      <c r="K20" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L20" s="0">
         <v>0</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="0">
         <v>100</v>
       </c>
       <c r="N20" s="7">
@@ -2797,16 +3440,16 @@
       <c r="B21" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="0">
         <v>95</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -2815,13 +3458,13 @@
       <c r="H21" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="K21" t="s">
-        <v>232</v>
-      </c>
-      <c r="L21">
+      <c r="K21" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L21" s="0">
         <v>0</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="0">
         <v>122</v>
       </c>
       <c r="N21" s="7">
@@ -2839,13 +3482,13 @@
       <c r="B22" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="0">
         <v>89</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -2854,13 +3497,19 @@
       <c r="H22" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="K22" t="s">
-        <v>232</v>
-      </c>
-      <c r="L22">
+      <c r="I22" t="s" s="0">
+        <v>549</v>
+      </c>
+      <c r="J22" t="s" s="0">
+        <v>550</v>
+      </c>
+      <c r="K22" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L22" s="0">
         <v>25</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="0">
         <v>74</v>
       </c>
       <c r="N22" s="7">
@@ -2878,28 +3527,34 @@
       <c r="B23" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" t="s" s="0">
         <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="K23" t="s">
-        <v>232</v>
-      </c>
-      <c r="L23">
+        <v>239</v>
+      </c>
+      <c r="I23" t="s" s="0">
+        <v>551</v>
+      </c>
+      <c r="J23" t="s" s="0">
+        <v>552</v>
+      </c>
+      <c r="K23" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L23" s="0">
         <v>0</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="0">
         <v>200</v>
       </c>
       <c r="N23" s="7">
@@ -2917,13 +3572,13 @@
       <c r="B24" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="0">
         <v>91</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -2932,13 +3587,19 @@
       <c r="H24" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="K24" t="s">
-        <v>232</v>
-      </c>
-      <c r="L24">
+      <c r="I24" t="s" s="0">
+        <v>553</v>
+      </c>
+      <c r="J24" t="s" s="0">
+        <v>554</v>
+      </c>
+      <c r="K24" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L24" s="0">
         <v>0</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="0">
         <v>177</v>
       </c>
       <c r="N24" s="7">
@@ -2956,28 +3617,34 @@
       <c r="B25" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" t="s" s="0">
         <v>92</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L25">
+        <v>555</v>
+      </c>
+      <c r="I25" t="s" s="0">
+        <v>556</v>
+      </c>
+      <c r="J25" t="s" s="0">
+        <v>557</v>
+      </c>
+      <c r="K25" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L25" s="0">
         <v>25</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="0">
         <v>42</v>
       </c>
       <c r="N25" s="7">
@@ -3001,16 +3668,16 @@
       <c r="B27" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="0">
         <v>32</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" t="s" s="0">
         <v>132</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -3019,13 +3686,19 @@
       <c r="H27" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K27" t="s">
-        <v>232</v>
-      </c>
-      <c r="L27">
+      <c r="I27" t="s" s="0">
+        <v>558</v>
+      </c>
+      <c r="J27" t="s" s="0">
+        <v>559</v>
+      </c>
+      <c r="K27" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L27" s="0">
         <v>0</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="0">
         <v>88</v>
       </c>
       <c r="N27" s="7">
@@ -3043,16 +3716,16 @@
       <c r="B28" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" t="s" s="0">
         <v>133</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -3061,13 +3734,19 @@
       <c r="H28" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="K28" t="s">
-        <v>232</v>
-      </c>
-      <c r="L28">
+      <c r="I28" t="s" s="0">
+        <v>560</v>
+      </c>
+      <c r="J28" t="s" s="0">
+        <v>561</v>
+      </c>
+      <c r="K28" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L28" s="0">
         <v>25</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="0">
         <v>101</v>
       </c>
       <c r="N28" s="7">
@@ -3085,31 +3764,31 @@
       <c r="B29" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" t="s" s="0">
         <v>134</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>488</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="K29" t="s">
-        <v>232</v>
-      </c>
-      <c r="L29">
+        <v>562</v>
+      </c>
+      <c r="K29" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L29" s="0">
         <v>0</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="0">
         <v>10</v>
       </c>
       <c r="N29" s="7">
@@ -3127,16 +3806,16 @@
       <c r="B30" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" t="s" s="0">
         <v>135</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -3145,13 +3824,19 @@
       <c r="H30" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="K30" t="s">
-        <v>232</v>
-      </c>
-      <c r="L30">
+      <c r="I30" t="s" s="0">
+        <v>563</v>
+      </c>
+      <c r="J30" t="s" s="0">
+        <v>564</v>
+      </c>
+      <c r="K30" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L30" s="0">
         <v>0</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="0">
         <v>78</v>
       </c>
       <c r="N30" s="7">
@@ -3169,16 +3854,16 @@
       <c r="B31" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" t="s" s="0">
         <v>136</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -3187,13 +3872,13 @@
       <c r="H31" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="K31" t="s">
-        <v>232</v>
-      </c>
-      <c r="L31">
+      <c r="K31" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L31" s="0">
         <v>0</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="0">
         <v>71</v>
       </c>
       <c r="N31" s="7">
@@ -3211,31 +3896,37 @@
       <c r="B32" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" t="s" s="0">
         <v>287</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" t="s" s="0">
         <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="K32" t="s">
-        <v>232</v>
-      </c>
-      <c r="L32">
+        <v>566</v>
+      </c>
+      <c r="I32" t="s" s="0">
+        <v>567</v>
+      </c>
+      <c r="J32" t="s" s="0">
+        <v>568</v>
+      </c>
+      <c r="K32" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L32" s="0">
         <v>0</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="0">
         <v>113</v>
       </c>
       <c r="N32" s="7">
@@ -3274,16 +3965,16 @@
       <c r="B36" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" t="s" s="0">
         <v>38</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" t="s" s="0">
         <v>125</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -3292,13 +3983,19 @@
       <c r="H36" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="K36" t="s">
-        <v>232</v>
-      </c>
-      <c r="L36">
+      <c r="I36" t="s" s="0">
+        <v>569</v>
+      </c>
+      <c r="J36" t="s" s="0">
+        <v>570</v>
+      </c>
+      <c r="K36" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L36" s="0">
         <v>25</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="0">
         <v>13</v>
       </c>
       <c r="N36" s="7">
@@ -3316,16 +4013,16 @@
       <c r="B37" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" t="s" s="0">
         <v>39</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" t="s" s="0">
         <v>140</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -3334,13 +4031,19 @@
       <c r="H37" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="K37" t="s">
-        <v>232</v>
-      </c>
-      <c r="L37">
+      <c r="I37" t="s" s="0">
+        <v>571</v>
+      </c>
+      <c r="J37" t="s" s="0">
+        <v>572</v>
+      </c>
+      <c r="K37" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L37" s="0">
         <v>0</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="0">
         <v>9</v>
       </c>
       <c r="N37" s="7">
@@ -3358,31 +4061,37 @@
       <c r="B38" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" t="s" s="0">
         <v>40</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" t="s" s="0">
         <v>109</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>490</v>
+        <v>573</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="K38" t="s">
-        <v>232</v>
-      </c>
-      <c r="L38">
+      <c r="I38" t="s" s="0">
+        <v>574</v>
+      </c>
+      <c r="J38" t="s" s="0">
+        <v>575</v>
+      </c>
+      <c r="K38" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L38" s="0">
         <v>0</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="0">
         <v>120</v>
       </c>
       <c r="N38" s="7">
@@ -3400,16 +4109,16 @@
       <c r="B39" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" t="s" s="0">
         <v>41</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" t="s" s="0">
         <v>109</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -3418,13 +4127,13 @@
       <c r="H39" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K39" t="s">
-        <v>232</v>
-      </c>
-      <c r="L39">
+      <c r="K39" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L39" s="0">
         <v>0</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="0">
         <v>116</v>
       </c>
       <c r="N39" s="7">
@@ -3442,16 +4151,16 @@
       <c r="B40" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" t="s" s="0">
         <v>144</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -3460,13 +4169,19 @@
       <c r="H40" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="K40" t="s">
-        <v>232</v>
-      </c>
-      <c r="L40">
+      <c r="I40" t="s" s="0">
+        <v>576</v>
+      </c>
+      <c r="J40" t="s" s="0">
+        <v>577</v>
+      </c>
+      <c r="K40" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L40" s="0">
         <v>0</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="0">
         <v>172</v>
       </c>
       <c r="N40" s="7">
@@ -3484,16 +4199,16 @@
       <c r="B41" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" t="s" s="0">
         <v>141</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -3502,13 +4217,19 @@
       <c r="H41" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="K41" t="s">
-        <v>232</v>
-      </c>
-      <c r="L41">
+      <c r="I41" t="s" s="0">
+        <v>578</v>
+      </c>
+      <c r="J41" t="s" s="0">
+        <v>579</v>
+      </c>
+      <c r="K41" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L41" s="0">
         <v>0</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="0">
         <v>79</v>
       </c>
       <c r="N41" s="7">
@@ -3526,31 +4247,37 @@
       <c r="B42" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" t="s" s="0">
         <v>44</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" t="s" s="0">
         <v>141</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>442</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="K42" t="s">
-        <v>232</v>
-      </c>
-      <c r="L42">
+        <v>580</v>
+      </c>
+      <c r="I42" t="s" s="0">
+        <v>581</v>
+      </c>
+      <c r="J42" t="s" s="0">
+        <v>582</v>
+      </c>
+      <c r="K42" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L42" s="0">
         <v>0</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="0">
         <v>118</v>
       </c>
       <c r="N42" s="7">
@@ -3568,16 +4295,16 @@
       <c r="B43" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" t="s" s="0">
         <v>45</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" t="s" s="0">
         <v>142</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -3586,13 +4313,19 @@
       <c r="H43" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="K43" t="s">
-        <v>232</v>
-      </c>
-      <c r="L43">
+      <c r="I43" t="s" s="0">
+        <v>583</v>
+      </c>
+      <c r="J43" t="s" s="0">
+        <v>584</v>
+      </c>
+      <c r="K43" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L43" s="0">
         <v>0</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="0">
         <v>154</v>
       </c>
       <c r="N43" s="7">
@@ -3610,31 +4343,31 @@
       <c r="B44" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" t="s" s="0">
         <v>142</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>490</v>
+        <v>573</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="K44" t="s">
-        <v>232</v>
-      </c>
-      <c r="L44">
+      <c r="K44" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L44" s="0">
         <v>0</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="0">
         <v>57</v>
       </c>
       <c r="N44" s="7">
@@ -3652,16 +4385,16 @@
       <c r="B45" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" t="s" s="0">
         <v>104</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" t="s" s="0">
         <v>143</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -3670,13 +4403,19 @@
       <c r="H45" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="K45" t="s">
-        <v>232</v>
-      </c>
-      <c r="L45">
+      <c r="I45" t="s" s="0">
+        <v>585</v>
+      </c>
+      <c r="J45" t="s" s="0">
+        <v>586</v>
+      </c>
+      <c r="K45" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L45" s="0">
         <v>0</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="0">
         <v>99</v>
       </c>
       <c r="N45" s="7">
@@ -3694,16 +4433,16 @@
       <c r="B46" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" t="s" s="0">
         <v>47</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" t="s" s="0">
         <v>95</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -3712,13 +4451,19 @@
       <c r="H46" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="K46" t="s">
-        <v>232</v>
-      </c>
-      <c r="L46">
+      <c r="I46" t="s" s="0">
+        <v>587</v>
+      </c>
+      <c r="J46" t="s" s="0">
+        <v>588</v>
+      </c>
+      <c r="K46" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L46" s="0">
         <v>0</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="0">
         <v>65</v>
       </c>
       <c r="N46" s="7">
@@ -3736,31 +4481,37 @@
       <c r="B47" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" t="s" s="0">
         <v>48</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" t="s" s="0">
         <v>85</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>186</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="K47" t="s">
-        <v>232</v>
-      </c>
-      <c r="L47">
+        <v>580</v>
+      </c>
+      <c r="I47" t="s" s="0">
+        <v>589</v>
+      </c>
+      <c r="J47" t="s" s="0">
+        <v>590</v>
+      </c>
+      <c r="K47" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L47" s="0">
         <v>0</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="0">
         <v>94</v>
       </c>
       <c r="N47" s="7">
@@ -3778,16 +4529,16 @@
       <c r="B48" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" t="s" s="0">
         <v>107</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" t="s" s="0">
         <v>85</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -3796,13 +4547,19 @@
       <c r="H48" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="K48" t="s">
-        <v>232</v>
-      </c>
-      <c r="L48">
+      <c r="I48" t="s" s="0">
+        <v>591</v>
+      </c>
+      <c r="J48" t="s" s="0">
+        <v>592</v>
+      </c>
+      <c r="K48" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L48" s="0">
         <v>25</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="0">
         <v>41</v>
       </c>
       <c r="N48" s="7">
@@ -3820,16 +4577,16 @@
       <c r="B49" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" t="s" s="0">
         <v>145</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -3838,13 +4595,19 @@
       <c r="H49" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="K49" t="s">
-        <v>232</v>
-      </c>
-      <c r="L49">
+      <c r="I49" t="s" s="0">
+        <v>593</v>
+      </c>
+      <c r="J49" t="s" s="0">
+        <v>594</v>
+      </c>
+      <c r="K49" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L49" s="0">
         <v>0</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="0">
         <v>192</v>
       </c>
       <c r="N49" s="7">
@@ -3862,31 +4625,31 @@
       <c r="B50" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" t="s" s="0">
         <v>276</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" t="s" s="0">
         <v>146</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>490</v>
+        <v>573</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="K50" t="s">
-        <v>232</v>
-      </c>
-      <c r="L50">
+      <c r="K50" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L50" s="0">
         <v>0</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="0">
         <v>88</v>
       </c>
       <c r="N50" s="7">
@@ -3904,16 +4667,16 @@
       <c r="B51" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" t="s" s="0">
         <v>87</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -3922,13 +4685,19 @@
       <c r="H51" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K51" t="s">
-        <v>232</v>
-      </c>
-      <c r="L51">
+      <c r="I51" t="s" s="0">
+        <v>595</v>
+      </c>
+      <c r="J51" t="s" s="0">
+        <v>596</v>
+      </c>
+      <c r="K51" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L51" s="0">
         <v>25</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="0">
         <v>157</v>
       </c>
       <c r="N51" s="7">
@@ -3946,31 +4715,37 @@
       <c r="B52" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" t="s" s="0">
         <v>87</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>190</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="K52" t="s">
-        <v>232</v>
-      </c>
-      <c r="L52">
+        <v>597</v>
+      </c>
+      <c r="I52" t="s" s="0">
+        <v>598</v>
+      </c>
+      <c r="J52" t="s" s="0">
+        <v>599</v>
+      </c>
+      <c r="K52" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L52" s="0">
         <v>0</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="0">
         <v>126</v>
       </c>
       <c r="N52" s="7">
@@ -3988,31 +4763,37 @@
       <c r="B53" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E53" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" t="s" s="0">
         <v>147</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>191</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="K53" t="s">
-        <v>232</v>
-      </c>
-      <c r="L53">
+        <v>600</v>
+      </c>
+      <c r="I53" t="s" s="0">
+        <v>601</v>
+      </c>
+      <c r="J53" t="s" s="0">
+        <v>602</v>
+      </c>
+      <c r="K53" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L53" s="0">
         <v>0</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="0">
         <v>184</v>
       </c>
       <c r="N53" s="7">
@@ -4030,16 +4811,16 @@
       <c r="B54" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" t="s" s="0">
         <v>278</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" t="s" s="0">
         <v>148</v>
       </c>
       <c r="G54" s="1" t="s">
@@ -4048,13 +4829,13 @@
       <c r="H54" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="K54" t="s">
-        <v>232</v>
-      </c>
-      <c r="L54">
+      <c r="K54" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L54" s="0">
         <v>25</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="0">
         <v>76</v>
       </c>
       <c r="N54" s="7">
@@ -4072,31 +4853,37 @@
       <c r="B55" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" t="s" s="0">
         <v>149</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>193</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="K55" t="s">
-        <v>232</v>
-      </c>
-      <c r="L55">
+        <v>603</v>
+      </c>
+      <c r="I55" t="s" s="0">
+        <v>604</v>
+      </c>
+      <c r="J55" t="s" s="0">
+        <v>605</v>
+      </c>
+      <c r="K55" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L55" s="0">
         <v>0</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="0">
         <v>44</v>
       </c>
       <c r="N55" s="7">
@@ -4138,31 +4925,31 @@
       <c r="B60" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" t="s" s="0">
         <v>150</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>491</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="K60" t="s">
-        <v>232</v>
-      </c>
-      <c r="L60">
+        <v>606</v>
+      </c>
+      <c r="K60" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L60" s="0">
         <v>0</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="0">
         <v>27</v>
       </c>
       <c r="N60" s="7">
@@ -4180,16 +4967,16 @@
       <c r="B61" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" t="s" s="0">
         <v>288</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" t="s" s="0">
         <v>93</v>
       </c>
       <c r="G61" s="1" t="s">
@@ -4198,13 +4985,13 @@
       <c r="H61" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="K61" t="s">
-        <v>232</v>
-      </c>
-      <c r="L61">
+      <c r="K61" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L61" s="0">
         <v>0</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="0">
         <v>167</v>
       </c>
       <c r="N61" s="7">
@@ -4222,31 +5009,37 @@
       <c r="B62" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" t="s" s="0">
         <v>107</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>194</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="K62" t="s">
-        <v>232</v>
-      </c>
-      <c r="L62">
+        <v>607</v>
+      </c>
+      <c r="I62" t="s" s="0">
+        <v>608</v>
+      </c>
+      <c r="J62" t="s" s="0">
+        <v>609</v>
+      </c>
+      <c r="K62" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L62" s="0">
         <v>25</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="0">
         <v>82</v>
       </c>
       <c r="N62" s="7">
@@ -4264,16 +5057,16 @@
       <c r="B63" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63" t="s" s="0">
         <v>113</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" t="s" s="0">
         <v>151</v>
       </c>
       <c r="G63" s="2" t="s">
@@ -4282,13 +5075,13 @@
       <c r="H63" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="K63" t="s">
-        <v>232</v>
-      </c>
-      <c r="L63">
+      <c r="K63" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L63" s="0">
         <v>0</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="0">
         <v>122</v>
       </c>
       <c r="N63" s="7">
@@ -4306,13 +5099,13 @@
       <c r="B64" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E64" t="s" s="0">
         <v>114</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -4321,13 +5114,19 @@
       <c r="H64" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="K64" t="s">
-        <v>232</v>
-      </c>
-      <c r="L64">
+      <c r="I64" t="s" s="0">
+        <v>610</v>
+      </c>
+      <c r="J64" t="s" s="0">
+        <v>611</v>
+      </c>
+      <c r="K64" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L64" s="0">
         <v>0</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="0">
         <v>92</v>
       </c>
       <c r="N64" s="7">
@@ -4345,13 +5144,13 @@
       <c r="B65" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65" t="s" s="0">
         <v>115</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -4360,13 +5159,19 @@
       <c r="H65" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="K65" t="s">
-        <v>232</v>
-      </c>
-      <c r="L65">
+      <c r="I65" t="s" s="0">
+        <v>612</v>
+      </c>
+      <c r="J65" t="s" s="0">
+        <v>613</v>
+      </c>
+      <c r="K65" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L65" s="0">
         <v>0</v>
       </c>
-      <c r="M65">
+      <c r="M65" s="0">
         <v>28</v>
       </c>
       <c r="N65" s="7">
@@ -4384,28 +5189,34 @@
       <c r="B66" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" t="s" s="0">
         <v>116</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>198</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="K66" t="s">
-        <v>232</v>
-      </c>
-      <c r="L66">
+        <v>614</v>
+      </c>
+      <c r="I66" t="s" s="0">
+        <v>615</v>
+      </c>
+      <c r="J66" t="s" s="0">
+        <v>616</v>
+      </c>
+      <c r="K66" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L66" s="0">
         <v>0</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="0">
         <v>6</v>
       </c>
       <c r="N66" s="7">
@@ -4423,16 +5234,16 @@
       <c r="B67" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F67" t="s" s="0">
         <v>85</v>
       </c>
       <c r="G67" s="2" t="s">
@@ -4441,13 +5252,13 @@
       <c r="H67" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K67" t="s">
-        <v>232</v>
-      </c>
-      <c r="L67">
+      <c r="K67" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L67" s="0">
         <v>0</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="0">
         <v>200</v>
       </c>
       <c r="N67" s="7">
@@ -4465,16 +5276,16 @@
       <c r="B68" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68" t="s" s="0">
         <v>117</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F68" t="s" s="0">
         <v>85</v>
       </c>
       <c r="G68" s="2" t="s">
@@ -4483,13 +5294,19 @@
       <c r="H68" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="K68" t="s">
-        <v>232</v>
-      </c>
-      <c r="L68">
+      <c r="I68" t="s" s="0">
+        <v>617</v>
+      </c>
+      <c r="J68" t="s" s="0">
+        <v>618</v>
+      </c>
+      <c r="K68" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L68" s="0">
         <v>0</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="0">
         <v>23</v>
       </c>
       <c r="N68" s="7">
@@ -4507,16 +5324,16 @@
       <c r="B69" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F69" t="s" s="0">
         <v>145</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -4525,13 +5342,19 @@
       <c r="H69" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="K69" t="s">
-        <v>232</v>
-      </c>
-      <c r="L69">
+      <c r="I69" t="s" s="0">
+        <v>619</v>
+      </c>
+      <c r="J69" t="s" s="0">
+        <v>620</v>
+      </c>
+      <c r="K69" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L69" s="0">
         <v>25</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="0">
         <v>183</v>
       </c>
       <c r="N69" s="7">
@@ -4549,16 +5372,16 @@
       <c r="B70" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F70" t="s" s="0">
         <v>146</v>
       </c>
       <c r="G70" s="2" t="s">
@@ -4567,13 +5390,19 @@
       <c r="H70" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="K70" t="s">
-        <v>232</v>
-      </c>
-      <c r="L70">
+      <c r="I70" t="s" s="0">
+        <v>621</v>
+      </c>
+      <c r="J70" t="s" s="0">
+        <v>622</v>
+      </c>
+      <c r="K70" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L70" s="0">
         <v>0</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="0">
         <v>73</v>
       </c>
       <c r="N70" s="7">
@@ -4591,31 +5420,37 @@
       <c r="B71" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71" t="s" s="0">
         <v>118</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F71" t="s" s="0">
         <v>87</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>202</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="K71" t="s">
-        <v>232</v>
-      </c>
-      <c r="L71">
+        <v>623</v>
+      </c>
+      <c r="I71" t="s" s="0">
+        <v>624</v>
+      </c>
+      <c r="J71" t="s" s="0">
+        <v>625</v>
+      </c>
+      <c r="K71" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L71" s="0">
         <v>0</v>
       </c>
-      <c r="M71">
+      <c r="M71" s="0">
         <v>180</v>
       </c>
       <c r="N71" s="7">
@@ -4633,16 +5468,16 @@
       <c r="B72" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" t="s" s="0">
         <v>286</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F72" t="s" s="0">
         <v>87</v>
       </c>
       <c r="G72" s="1" t="s">
@@ -4651,13 +5486,13 @@
       <c r="H72" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="K72" t="s">
-        <v>232</v>
-      </c>
-      <c r="L72">
+      <c r="K72" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L72" s="0">
         <v>0</v>
       </c>
-      <c r="M72">
+      <c r="M72" s="0">
         <v>187</v>
       </c>
       <c r="N72" s="7">
@@ -4675,31 +5510,37 @@
       <c r="B73" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="F73" t="s">
+      <c r="F73" t="s" s="0">
         <v>147</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>203</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="K73" t="s">
-        <v>232</v>
-      </c>
-      <c r="L73">
+        <v>626</v>
+      </c>
+      <c r="I73" t="s" s="0">
+        <v>627</v>
+      </c>
+      <c r="J73" t="s" s="0">
+        <v>628</v>
+      </c>
+      <c r="K73" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L73" s="0">
         <v>0</v>
       </c>
-      <c r="M73">
+      <c r="M73" s="0">
         <v>18</v>
       </c>
       <c r="N73" s="7">
@@ -4717,16 +5558,16 @@
       <c r="B74" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" t="s" s="0">
         <v>148</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -4735,13 +5576,19 @@
       <c r="H74" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="K74" t="s">
-        <v>232</v>
-      </c>
-      <c r="L74">
+      <c r="I74" t="s" s="0">
+        <v>629</v>
+      </c>
+      <c r="J74" t="s" s="0">
+        <v>630</v>
+      </c>
+      <c r="K74" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L74" s="0">
         <v>25</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="0">
         <v>109</v>
       </c>
       <c r="N74" s="7">
@@ -4759,31 +5606,37 @@
       <c r="B75" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F75" t="s" s="0">
         <v>149</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>205</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="K75" t="s">
-        <v>232</v>
-      </c>
-      <c r="L75">
+        <v>631</v>
+      </c>
+      <c r="I75" t="s" s="0">
+        <v>632</v>
+      </c>
+      <c r="J75" t="s" s="0">
+        <v>633</v>
+      </c>
+      <c r="K75" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L75" s="0">
         <v>0</v>
       </c>
-      <c r="M75">
+      <c r="M75" s="0">
         <v>12</v>
       </c>
       <c r="N75" s="7">
@@ -4801,31 +5654,37 @@
       <c r="B76" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" t="s" s="0">
         <v>289</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" t="s" s="0">
         <v>152</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>494</v>
+        <v>634</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="K76" t="s">
-        <v>232</v>
-      </c>
-      <c r="L76">
+      <c r="I76" t="s" s="0">
+        <v>635</v>
+      </c>
+      <c r="J76" t="s" s="0">
+        <v>636</v>
+      </c>
+      <c r="K76" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L76" s="0">
         <v>0</v>
       </c>
-      <c r="M76">
+      <c r="M76" s="0">
         <v>174</v>
       </c>
       <c r="N76" s="7">
@@ -4843,31 +5702,37 @@
       <c r="B77" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="F77" t="s">
+      <c r="F77" t="s" s="0">
         <v>153</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>493</v>
+        <v>637</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="K77" t="s">
-        <v>232</v>
-      </c>
-      <c r="L77">
+        <v>638</v>
+      </c>
+      <c r="I77" t="s" s="0">
+        <v>639</v>
+      </c>
+      <c r="J77" t="s" s="0">
+        <v>640</v>
+      </c>
+      <c r="K77" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L77" s="0">
         <v>0</v>
       </c>
-      <c r="M77">
+      <c r="M77" s="0">
         <v>112</v>
       </c>
       <c r="N77" s="7">
@@ -4891,31 +5756,37 @@
       <c r="B79" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="F79" t="s">
+      <c r="F79" t="s" s="0">
         <v>154</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>206</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="K79" t="s">
-        <v>232</v>
-      </c>
-      <c r="L79">
+        <v>641</v>
+      </c>
+      <c r="I79" t="s" s="0">
+        <v>642</v>
+      </c>
+      <c r="J79" t="s" s="0">
+        <v>643</v>
+      </c>
+      <c r="K79" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L79" s="0">
         <v>0</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="0">
         <v>121</v>
       </c>
       <c r="N79" s="7">
@@ -4933,31 +5804,37 @@
       <c r="B80" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F80" t="s">
+      <c r="F80" t="s" s="0">
         <v>150</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>207</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="K80" t="s">
-        <v>232</v>
-      </c>
-      <c r="L80">
+        <v>644</v>
+      </c>
+      <c r="I80" t="s" s="0">
+        <v>645</v>
+      </c>
+      <c r="J80" t="s" s="0">
+        <v>646</v>
+      </c>
+      <c r="K80" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L80" s="0">
         <v>25</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="0">
         <v>146</v>
       </c>
       <c r="N80" s="7">
@@ -4975,16 +5852,16 @@
       <c r="B81" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" t="s" s="0">
         <v>279</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" t="s" s="0">
         <v>93</v>
       </c>
       <c r="G81" s="1" t="s">
@@ -4993,13 +5870,19 @@
       <c r="H81" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="K81" t="s">
-        <v>232</v>
-      </c>
-      <c r="L81">
+      <c r="I81" t="s" s="0">
+        <v>647</v>
+      </c>
+      <c r="J81" t="s" s="0">
+        <v>648</v>
+      </c>
+      <c r="K81" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L81" s="0">
         <v>0</v>
       </c>
-      <c r="M81">
+      <c r="M81" s="0">
         <v>139</v>
       </c>
       <c r="N81" s="7">
@@ -5017,31 +5900,37 @@
       <c r="B82" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" t="s" s="0">
         <v>61</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" t="s" s="0">
         <v>107</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>209</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="K82" t="s">
-        <v>232</v>
-      </c>
-      <c r="L82">
+        <v>649</v>
+      </c>
+      <c r="I82" t="s" s="0">
+        <v>650</v>
+      </c>
+      <c r="J82" t="s" s="0">
+        <v>651</v>
+      </c>
+      <c r="K82" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L82" s="0">
         <v>0</v>
       </c>
-      <c r="M82">
+      <c r="M82" s="0">
         <v>6</v>
       </c>
       <c r="N82" s="7">
@@ -5059,31 +5948,31 @@
       <c r="B83" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" t="s" s="0">
         <v>287</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="F83" t="s">
+      <c r="F83" t="s" s="0">
         <v>151</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>210</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K83" t="s">
-        <v>232</v>
-      </c>
-      <c r="L83">
+        <v>652</v>
+      </c>
+      <c r="K83" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L83" s="0">
         <v>0</v>
       </c>
-      <c r="M83">
+      <c r="M83" s="0">
         <v>63</v>
       </c>
       <c r="N83" s="7">
@@ -5101,13 +5990,13 @@
       <c r="B84" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" t="s" s="0">
         <v>63</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84" t="s" s="0">
         <v>85</v>
       </c>
       <c r="G84" s="1" t="s">
@@ -5116,13 +6005,19 @@
       <c r="H84" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="K84" t="s">
-        <v>232</v>
-      </c>
-      <c r="L84">
+      <c r="I84" t="s" s="0">
+        <v>653</v>
+      </c>
+      <c r="J84" t="s" s="0">
+        <v>654</v>
+      </c>
+      <c r="K84" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L84" s="0">
         <v>0</v>
       </c>
-      <c r="M84">
+      <c r="M84" s="0">
         <v>123</v>
       </c>
       <c r="N84" s="7">
@@ -5147,16 +6042,16 @@
       <c r="B86" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" t="s" s="0">
         <v>64</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="F86" t="s">
+      <c r="F86" t="s" s="0">
         <v>155</v>
       </c>
       <c r="G86" s="1" t="s">
@@ -5165,13 +6060,19 @@
       <c r="H86" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="K86" t="s">
-        <v>232</v>
-      </c>
-      <c r="L86">
+      <c r="I86" t="s" s="0">
+        <v>655</v>
+      </c>
+      <c r="J86" t="s" s="0">
+        <v>656</v>
+      </c>
+      <c r="K86" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L86" s="0">
         <v>25</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="0">
         <v>170</v>
       </c>
       <c r="N86" s="7">
@@ -5189,16 +6090,16 @@
       <c r="B87" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" t="s" s="0">
         <v>65</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87" t="s" s="0">
         <v>128</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F87" t="s" s="0">
         <v>156</v>
       </c>
       <c r="G87" s="1" t="s">
@@ -5207,13 +6108,19 @@
       <c r="H87" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="K87" t="s">
-        <v>232</v>
-      </c>
-      <c r="L87">
+      <c r="I87" t="s" s="0">
+        <v>657</v>
+      </c>
+      <c r="J87" t="s" s="0">
+        <v>658</v>
+      </c>
+      <c r="K87" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L87" s="0">
         <v>0</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="0">
         <v>171</v>
       </c>
       <c r="N87" s="7">
@@ -5231,31 +6138,37 @@
       <c r="B88" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F88" t="s" s="0">
         <v>157</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>214</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="K88" t="s">
-        <v>232</v>
-      </c>
-      <c r="L88">
+        <v>659</v>
+      </c>
+      <c r="I88" t="s" s="0">
+        <v>660</v>
+      </c>
+      <c r="J88" t="s" s="0">
+        <v>661</v>
+      </c>
+      <c r="K88" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L88" s="0">
         <v>0</v>
       </c>
-      <c r="M88">
+      <c r="M88" s="0">
         <v>93</v>
       </c>
       <c r="N88" s="7">
@@ -5273,31 +6186,37 @@
       <c r="B89" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" t="s" s="0">
         <v>129</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" t="s" s="0">
         <v>158</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>215</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="K89" t="s">
-        <v>232</v>
-      </c>
-      <c r="L89">
+        <v>662</v>
+      </c>
+      <c r="I89" t="s" s="0">
+        <v>663</v>
+      </c>
+      <c r="J89" t="s" s="0">
+        <v>664</v>
+      </c>
+      <c r="K89" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L89" s="0">
         <v>0</v>
       </c>
-      <c r="M89">
+      <c r="M89" s="0">
         <v>40</v>
       </c>
       <c r="N89" s="7">
@@ -5315,13 +6234,13 @@
       <c r="B90" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" t="s" s="0">
         <v>283</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90" t="s" s="0">
         <v>130</v>
       </c>
       <c r="G90" s="1" t="s">
@@ -5330,13 +6249,13 @@
       <c r="H90" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="K90" t="s">
-        <v>232</v>
-      </c>
-      <c r="L90">
+      <c r="K90" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L90" s="0">
         <v>0</v>
       </c>
-      <c r="M90">
+      <c r="M90" s="0">
         <v>118</v>
       </c>
       <c r="N90" s="7">
@@ -5354,16 +6273,16 @@
       <c r="B91" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" t="s" s="0">
         <v>290</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F91" t="s">
+      <c r="F91" t="s" s="0">
         <v>159</v>
       </c>
       <c r="G91" s="1" t="s">
@@ -5372,13 +6291,19 @@
       <c r="H91" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K91" t="s">
-        <v>232</v>
-      </c>
-      <c r="L91">
+      <c r="I91" t="s" s="0">
+        <v>665</v>
+      </c>
+      <c r="J91" t="s" s="0">
+        <v>666</v>
+      </c>
+      <c r="K91" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L91" s="0">
         <v>0</v>
       </c>
-      <c r="M91">
+      <c r="M91" s="0">
         <v>125</v>
       </c>
       <c r="N91" s="7">
@@ -5396,31 +6321,37 @@
       <c r="B92" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="F92" t="s">
+      <c r="F92" t="s" s="0">
         <v>160</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>217</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="K92" t="s">
-        <v>232</v>
-      </c>
-      <c r="L92">
+        <v>667</v>
+      </c>
+      <c r="I92" t="s" s="0">
+        <v>668</v>
+      </c>
+      <c r="J92" t="s" s="0">
+        <v>669</v>
+      </c>
+      <c r="K92" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L92" s="0">
         <v>0</v>
       </c>
-      <c r="M92">
+      <c r="M92" s="0">
         <v>56</v>
       </c>
       <c r="N92" s="7">
@@ -5439,31 +6370,37 @@
       <c r="B93" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="F93" t="s">
+      <c r="F93" t="s" s="0">
         <v>161</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>218</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="K93" t="s">
-        <v>232</v>
-      </c>
-      <c r="L93">
+        <v>670</v>
+      </c>
+      <c r="I93" t="s" s="0">
+        <v>671</v>
+      </c>
+      <c r="J93" t="s" s="0">
+        <v>672</v>
+      </c>
+      <c r="K93" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L93" s="0">
         <v>25</v>
       </c>
-      <c r="M93">
+      <c r="M93" s="0">
         <v>88</v>
       </c>
       <c r="N93" s="7">
@@ -5481,29 +6418,29 @@
       <c r="B94" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" t="s" s="0">
         <v>83</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="K94" t="s">
-        <v>232</v>
-      </c>
-      <c r="L94">
+        <v>673</v>
+      </c>
+      <c r="K94" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L94" s="0">
         <v>0</v>
       </c>
-      <c r="M94">
+      <c r="M94" s="0">
         <v>116</v>
       </c>
       <c r="N94" s="7">
@@ -5521,16 +6458,16 @@
       <c r="B95" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" t="s" s="0">
         <v>72</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="F95" t="s">
+      <c r="F95" t="s" s="0">
         <v>83</v>
       </c>
       <c r="G95" s="1" t="s">
@@ -5539,13 +6476,19 @@
       <c r="H95" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K95" t="s">
-        <v>232</v>
-      </c>
-      <c r="L95">
+      <c r="I95" t="s" s="0">
+        <v>674</v>
+      </c>
+      <c r="J95" t="s" s="0">
+        <v>675</v>
+      </c>
+      <c r="K95" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L95" s="0">
         <v>0</v>
       </c>
-      <c r="M95">
+      <c r="M95" s="0">
         <v>31</v>
       </c>
       <c r="N95" s="7">
@@ -5605,31 +6548,37 @@
       <c r="B102" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" t="s" s="0">
         <v>130</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F102" t="s" s="0">
         <v>162</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>220</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="K102" t="s">
-        <v>232</v>
-      </c>
-      <c r="L102">
+        <v>676</v>
+      </c>
+      <c r="I102" t="s" s="0">
+        <v>677</v>
+      </c>
+      <c r="J102" t="s" s="0">
+        <v>678</v>
+      </c>
+      <c r="K102" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L102" s="0">
         <v>0</v>
       </c>
-      <c r="M102">
+      <c r="M102" s="0">
         <v>17</v>
       </c>
       <c r="N102" s="7">
@@ -5647,16 +6596,16 @@
       <c r="B103" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" t="s" s="0">
         <v>285</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" t="s" s="0">
         <v>101</v>
       </c>
-      <c r="F103" t="s">
+      <c r="F103" t="s" s="0">
         <v>163</v>
       </c>
       <c r="G103" s="2" t="s">
@@ -5665,13 +6614,19 @@
       <c r="H103" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="K103" t="s">
-        <v>232</v>
-      </c>
-      <c r="L103">
+      <c r="I103" t="s" s="0">
+        <v>679</v>
+      </c>
+      <c r="J103" t="s" s="0">
+        <v>680</v>
+      </c>
+      <c r="K103" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L103" s="0">
         <v>25</v>
       </c>
-      <c r="M103">
+      <c r="M103" s="0">
         <v>52</v>
       </c>
       <c r="N103" s="7">
@@ -5689,16 +6644,16 @@
       <c r="B104" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" t="s" s="0">
         <v>291</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="F104" t="s">
+      <c r="F104" t="s" s="0">
         <v>164</v>
       </c>
       <c r="G104" s="1" t="s">
@@ -5707,13 +6662,19 @@
       <c r="H104" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K104" t="s">
-        <v>232</v>
-      </c>
-      <c r="L104">
+      <c r="I104" t="s" s="0">
+        <v>681</v>
+      </c>
+      <c r="J104" t="s" s="0">
+        <v>682</v>
+      </c>
+      <c r="K104" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L104" s="0">
         <v>0</v>
       </c>
-      <c r="M104">
+      <c r="M104" s="0">
         <v>135</v>
       </c>
       <c r="N104" s="7">
@@ -5731,16 +6692,16 @@
       <c r="B105" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105" t="s" s="0">
         <v>131</v>
       </c>
-      <c r="F105" t="s">
+      <c r="F105" t="s" s="0">
         <v>79</v>
       </c>
       <c r="G105" s="1" t="s">
@@ -5749,13 +6710,13 @@
       <c r="H105" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="K105" t="s">
-        <v>232</v>
-      </c>
-      <c r="L105">
+      <c r="K105" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L105" s="0">
         <v>0</v>
       </c>
-      <c r="M105">
+      <c r="M105" s="0">
         <v>6</v>
       </c>
       <c r="N105" s="7">
@@ -5773,31 +6734,37 @@
       <c r="B106" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" t="s" s="0">
         <v>292</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" t="s" s="0">
         <v>11</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F106" t="s" s="0">
         <v>93</v>
       </c>
       <c r="G106" s="1" t="s">
         <v>224</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="K106" t="s">
-        <v>232</v>
-      </c>
-      <c r="L106">
+        <v>683</v>
+      </c>
+      <c r="I106" t="s" s="0">
+        <v>684</v>
+      </c>
+      <c r="J106" t="s" s="0">
+        <v>685</v>
+      </c>
+      <c r="K106" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L106" s="0">
         <v>25</v>
       </c>
-      <c r="M106">
+      <c r="M106" s="0">
         <v>127</v>
       </c>
       <c r="N106" s="7">
@@ -5955,31 +6922,31 @@
       <c r="B127" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" t="s" s="0">
         <v>273</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" t="s" s="0">
         <v>73</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="F127" t="s">
+      <c r="F127" t="s" s="0">
         <v>165</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>218</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="K127" t="s">
-        <v>232</v>
-      </c>
-      <c r="L127">
+        <v>686</v>
+      </c>
+      <c r="K127" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L127" s="0">
         <v>0</v>
       </c>
-      <c r="M127">
+      <c r="M127" s="0">
         <v>95</v>
       </c>
       <c r="N127" s="7">
@@ -5997,31 +6964,37 @@
       <c r="B128" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" t="s" s="0">
         <v>280</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" t="s" s="0">
         <v>74</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" t="s" s="0">
         <v>120</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F128" t="s" s="0">
         <v>166</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>225</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="K128" t="s">
-        <v>232</v>
-      </c>
-      <c r="L128">
+        <v>687</v>
+      </c>
+      <c r="I128" t="s" s="0">
+        <v>688</v>
+      </c>
+      <c r="J128" t="s" s="0">
+        <v>689</v>
+      </c>
+      <c r="K128" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L128" s="0">
         <v>0</v>
       </c>
-      <c r="M128">
+      <c r="M128" s="0">
         <v>195</v>
       </c>
       <c r="N128" s="7">
@@ -6039,31 +7012,37 @@
       <c r="B129" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" t="s" s="0">
         <v>75</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" t="s" s="0">
         <v>121</v>
       </c>
-      <c r="F129" t="s">
+      <c r="F129" t="s" s="0">
         <v>167</v>
       </c>
       <c r="G129" s="2" t="s">
         <v>226</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="K129" t="s">
-        <v>232</v>
-      </c>
-      <c r="L129">
+        <v>690</v>
+      </c>
+      <c r="I129" t="s" s="0">
+        <v>691</v>
+      </c>
+      <c r="J129" t="s" s="0">
+        <v>692</v>
+      </c>
+      <c r="K129" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L129" s="0">
         <v>0</v>
       </c>
-      <c r="M129">
+      <c r="M129" s="0">
         <v>117</v>
       </c>
       <c r="N129" s="7">
@@ -6081,31 +7060,31 @@
       <c r="B130" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" t="s" s="0">
         <v>81</v>
       </c>
-      <c r="F130" t="s">
+      <c r="F130" t="s" s="0">
         <v>168</v>
       </c>
       <c r="G130" s="1" t="s">
         <v>226</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="K130" t="s">
-        <v>232</v>
-      </c>
-      <c r="L130">
+        <v>693</v>
+      </c>
+      <c r="K130" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L130" s="0">
         <v>25</v>
       </c>
-      <c r="M130">
+      <c r="M130" s="0">
         <v>36</v>
       </c>
       <c r="N130" s="7">
@@ -6123,31 +7102,37 @@
       <c r="B131" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" t="s" s="0">
         <v>122</v>
       </c>
-      <c r="F131" t="s">
+      <c r="F131" t="s" s="0">
         <v>169</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>227</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="K131" t="s">
-        <v>232</v>
-      </c>
-      <c r="L131">
+        <v>694</v>
+      </c>
+      <c r="I131" t="s" s="0">
+        <v>695</v>
+      </c>
+      <c r="J131" t="s" s="0">
+        <v>696</v>
+      </c>
+      <c r="K131" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L131" s="0">
         <v>0</v>
       </c>
-      <c r="M131">
+      <c r="M131" s="0">
         <v>54</v>
       </c>
       <c r="N131" s="7">
@@ -6165,31 +7150,37 @@
       <c r="B132" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="F132" t="s">
+      <c r="F132" t="s" s="0">
         <v>170</v>
       </c>
       <c r="G132" s="1" t="s">
         <v>228</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K132" t="s">
+        <v>697</v>
+      </c>
+      <c r="I132" t="s" s="0">
+        <v>698</v>
+      </c>
+      <c r="J132" t="s" s="0">
+        <v>699</v>
+      </c>
+      <c r="K132" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="L132">
+      <c r="L132" s="0">
         <v>0</v>
       </c>
-      <c r="M132">
+      <c r="M132" s="0">
         <v>76</v>
       </c>
       <c r="N132" s="7">
@@ -6207,31 +7198,37 @@
       <c r="B133" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" t="s" s="0">
         <v>68</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F133" t="s" s="0">
         <v>162</v>
       </c>
       <c r="G133" s="1" t="s">
         <v>229</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="K133" t="s">
-        <v>232</v>
-      </c>
-      <c r="L133">
+        <v>700</v>
+      </c>
+      <c r="I133" t="s" s="0">
+        <v>701</v>
+      </c>
+      <c r="J133" t="s" s="0">
+        <v>702</v>
+      </c>
+      <c r="K133" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L133" s="0">
         <v>0</v>
       </c>
-      <c r="M133">
+      <c r="M133" s="0">
         <v>67</v>
       </c>
       <c r="N133" s="7">
@@ -6249,31 +7246,37 @@
       <c r="B134" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" t="s" s="0">
         <v>274</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" t="s" s="0">
         <v>69</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" t="s" s="0">
         <v>124</v>
       </c>
-      <c r="F134" t="s">
+      <c r="F134" t="s" s="0">
         <v>163</v>
       </c>
       <c r="G134" s="1" t="s">
         <v>230</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="K134" t="s">
-        <v>232</v>
-      </c>
-      <c r="L134">
+        <v>703</v>
+      </c>
+      <c r="I134" t="s" s="0">
+        <v>704</v>
+      </c>
+      <c r="J134" t="s" s="0">
+        <v>705</v>
+      </c>
+      <c r="K134" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L134" s="0">
         <v>25</v>
       </c>
-      <c r="M134">
+      <c r="M134" s="0">
         <v>110</v>
       </c>
       <c r="N134" s="7">
@@ -6291,29 +7294,29 @@
       <c r="B135" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" t="s" s="0">
         <v>293</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" t="s" s="0">
         <v>70</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="F135" t="s">
+      <c r="F135" t="s" s="0">
         <v>164</v>
       </c>
       <c r="G135" s="1"/>
       <c r="H135" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="K135" t="s">
-        <v>232</v>
-      </c>
-      <c r="L135">
+        <v>706</v>
+      </c>
+      <c r="K135" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L135" s="0">
         <v>0</v>
       </c>
-      <c r="M135">
+      <c r="M135" s="0">
         <v>160</v>
       </c>
       <c r="N135" s="7">
@@ -6331,31 +7334,37 @@
       <c r="B136" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" t="s" s="0">
         <v>284</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" t="s" s="0">
         <v>71</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" t="s" s="0">
         <v>125</v>
       </c>
-      <c r="F136" t="s">
+      <c r="F136" t="s" s="0">
         <v>79</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>231</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="K136" t="s">
-        <v>232</v>
-      </c>
-      <c r="L136">
+        <v>707</v>
+      </c>
+      <c r="I136" t="s" s="0">
+        <v>708</v>
+      </c>
+      <c r="J136" t="s" s="0">
+        <v>709</v>
+      </c>
+      <c r="K136" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="L136" s="0">
         <v>0</v>
       </c>
-      <c r="M136">
+      <c r="M136" s="0">
         <v>17</v>
       </c>
       <c r="N136" s="7">
@@ -6439,693 +7448,693 @@
   <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="11" max="12" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" customWidth="true" width="46.0"/>
+    <col min="5" max="5" customWidth="true" width="15.85546875"/>
+    <col min="6" max="6" customWidth="true" width="14.85546875"/>
+    <col min="7" max="7" customWidth="true" width="14.28515625"/>
+    <col min="11" max="12" customWidth="true" width="20.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>380</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>384</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>385</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>381</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>396</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>378</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>386</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>419</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>420</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>387</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>394</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>379</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="0">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>406</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>433</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>20</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>435</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <v>10</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="0">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="0">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="0">
         <v>427</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="0">
         <v>10</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="0">
         <v>2</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="0">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G5" t="s">
-        <v>232</v>
-      </c>
-      <c r="H5">
+      <c r="G5" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="H5" s="0">
         <v>20</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <v>0</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="0">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I6">
+      <c r="G6" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I6" s="0">
         <v>20</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <v>0.2</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="0">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="0">
         <v>423</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I7">
+      <c r="G7" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I7" s="0">
         <v>50</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="0">
         <v>0.3</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="0">
         <v>11</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G8" t="s">
-        <v>232</v>
-      </c>
-      <c r="I8">
+      <c r="G8" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I8" s="0">
         <v>50</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="0">
         <v>1</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="0">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="0">
         <v>425</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G9" t="s">
-        <v>232</v>
-      </c>
-      <c r="I9">
+      <c r="G9" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I9" s="0">
         <v>100</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="0">
         <v>2</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="0">
         <v>11</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="0">
         <v>409</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="0">
         <v>382</v>
       </c>
-      <c r="G10" t="s">
-        <v>232</v>
-      </c>
-      <c r="I10">
+      <c r="G10" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="I10" s="0">
         <v>999</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="0">
         <v>5</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="0">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="0">
         <v>393</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="0">
         <v>10</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="0">
         <v>14</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="0">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="0">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="0">
         <v>429</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="0">
         <v>10</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="0">
         <v>25</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="0">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="0">
         <v>389</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="0">
         <v>50</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="0">
         <v>10</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="0">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="0">
         <v>390</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="0">
         <v>422</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="0">
         <v>30</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="0">
         <v>1</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="0">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="0">
         <v>391</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="0">
         <v>423</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="0">
         <v>20</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="0">
         <v>2</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="0">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="0">
         <v>392</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="0">
         <v>424</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="0">
         <v>50</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="0">
         <v>5</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="0">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="0">
         <v>401</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="0">
         <v>425</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="0">
         <v>50</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="0">
         <v>10</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="0">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="0">
         <v>404</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="0">
         <v>426</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="0">
         <v>408</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="0">
         <v>402</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="0">
         <v>400</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="0">
         <v>9999</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="0">
         <v>20</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="0">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="0">
         <v>428</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="0">
         <v>429</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="0">
         <v>10</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="0">
         <v>16</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="0">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="0">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="0">
         <v>421</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="0">
         <v>383</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="0">
         <v>399</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="G20" t="s">
-        <v>232</v>
-      </c>
-      <c r="H20">
+      <c r="G20" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="H20" s="0">
         <v>15</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="0">
         <v>10</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="0">
         <v>1</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="0">
         <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="0">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="0">
         <v>432</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="0">
         <v>388</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="0">
         <v>434</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="0">
         <v>30</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="0">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="0">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="0">
         <v>407</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="0">
         <v>430</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="0">
         <v>431</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="0">
         <v>403</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="s" s="0">
         <v>398</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="0">
         <v>15</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="0">
         <v>21</v>
       </c>
     </row>

--- a/src/main/resources/SistemasBasura.xlsx
+++ b/src/main/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>

--- a/src/main/resources/SistemasBasura.xlsx
+++ b/src/main/resources/SistemasBasura.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="710">
   <si>
     <t>Nombre</t>
   </si>
